--- a/utils/monday_sprint_sprint_2026-10.xlsx
+++ b/utils/monday_sprint_sprint_2026-10.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="421">
   <si>
     <t>Ticket</t>
   </si>
@@ -87,7 +87,7 @@
     <t>26/02/2026</t>
   </si>
   <si>
-    <t>15/04/2026</t>
+    <t>10/04/2026</t>
   </si>
   <si>
     <t>Feito</t>
@@ -117,672 +117,660 @@
     <t>22/01/2026</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>36648</t>
+  </si>
+  <si>
+    <t>Causa Raiz - BI retrabalho TT - Reunião</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Precisamos incluir no banco de dados do BI do retrabalho de Tratamento Térmico a causa raiz do retrabalho. Essa informação é crucial para usar o BI de forma integral, sem necessidade de suporte de excel paralelo. Atualmente no excel tenho o banco de dados dessa maneira: DIA MÊS MÊS EXTENSO </t>
+  </si>
+  <si>
+    <t>Gilberto José Rebelo Junior</t>
+  </si>
+  <si>
+    <t>13/02/2026</t>
+  </si>
+  <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>37006</t>
+  </si>
+  <si>
+    <t>Qlik - Inclusão de campos novos qvd</t>
+  </si>
+  <si>
+    <t>Boa tarde Gentileza atualizar os qvds conforme abaixo: * Atualizar o qvd CPC389 com o campo novo abaixo "Motivo Modal Aéreo": [lib://Qlik Files - Root/QVD/EXTRACAO/CPC389.qvd] * Atualizar o qvd CTEEMIT com o campo novo abaixo "Data de Entrega" e "Frete dedicadop/ atraso": [lib://Qlik Files - Root/QV</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>36467</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Sitema retrabalho ajustagem com erro</t>
+  </si>
+  <si>
+    <t>Boa tarde! Enviando para o Email correto. Gentileza considerar o e-mail abaixo. Atenciosamente, De: Fernanda da Costa Rodrigues Enviada em: quarta-feira, 4 de fevereiro de 2026 14:25 Para: 'Suporte Altona' Cc: Edson João Hammermeister ; Lucas José Sebold Assunto: RES: Resolvido: Sitema retrabalho aj</t>
+  </si>
+  <si>
+    <t>Fernanda da Costa Rodrigues</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>36233</t>
+  </si>
+  <si>
+    <t>Automatizar apontamento dos mantenedores</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito um chamado para fazer automatização dos dados Hora ponto X Horas apontadas, com uma média mínima de 75% de apontamento. E ao mesmo tempo uma análise de total de ordens baixadas, ordens pendentes e somatório das ordens (baixadas/pendentes). Em anexos, está um modelo que estamos us</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>23/01/2026</t>
+  </si>
+  <si>
+    <t>36454</t>
+  </si>
+  <si>
+    <t>Inclusão de Corrida/forno/ano</t>
+  </si>
+  <si>
+    <t>Bom dia, Seria possível incluir na Tabela de linhas de produção no QlikSense a corrida, forno e ano de aciaria, isso facilita na analise de dados para o retrabalho de tratamento térmico, já que temos que tratar todas por corrida, e a reprova desses ensaios causa o retrabalhar todas as peças da corri</t>
+  </si>
+  <si>
+    <t>Eduardo Basso Pinto</t>
+  </si>
+  <si>
+    <t>36863</t>
+  </si>
+  <si>
+    <t>Aplicação QlikSense com dados do MESS</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito um chamado para que a aplicação do QlikSense comece a utilizar os dados do MESS para que possamos analisar os dados lançados. Aba da aplicação em anexo.</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>36299</t>
+  </si>
+  <si>
+    <t>Calcular indicadores através dos dados do CRP</t>
+  </si>
+  <si>
+    <t>Bom dia, Quero solicitar um chamado para que os cálculos do MTTR, MDT, MTBF e Disponibilidade de Máquina sejam calculados através dados Usinagem IROG - Operações de manutenções, pois são atualizados diariamente. E através disto criar um compartimento deles para que fiquem visíveis na mesma aba confo</t>
+  </si>
+  <si>
+    <t>28/01/2026</t>
+  </si>
+  <si>
+    <t>35467</t>
+  </si>
+  <si>
+    <t>Alterar Cálculo do Custo de SUCATA RETORNO</t>
+  </si>
+  <si>
+    <t>Bom dia a todos! O processo de controle dos estoques de SUCATA RETORNO está em aprimoramento, para tanto, é preciso implementar alterações de sistema válidas a partir de 01/01/2026: Segue forma de cálculo: 1. Entrada em estoque a partir Corte de Canal. * Peso a ser considerado para Entrada, peso ali</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>27/11/2025</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>23773</t>
+  </si>
+  <si>
+    <t>Problema</t>
+  </si>
+  <si>
+    <t>Registro de moldagem USE/ULE</t>
+  </si>
+  <si>
+    <t>Bom dia, Estamos tendo inconsistência nos registros de Moldagem USE/ULE, acontece às vezes do registro ser finalizado e a movimentação não ocorrer. Ocorre tanto na ULE como na USE. Exemplos abaixo: Duvidas entrar em contato. Att.</t>
+  </si>
+  <si>
+    <t>Darlan Pressi</t>
+  </si>
+  <si>
+    <t>19/12/2023</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>35426</t>
+  </si>
+  <si>
+    <t>Ajustar quem pode movimentar</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor revisar as permissões dos setores de amostra conforme abaixo. Esse setores são apenas para os membros da minha equipe, pois os demais não tem conhecimento para poder movimentá-los. Setor 596 - LIBERAÇÃO DE AMOSTRAS Remover 144773 e 145261 Setor 597 - FECHAMENTO DE AMOSTRAS Remover 1</t>
+  </si>
+  <si>
+    <t>Paula Rosa M. Grando</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>36724</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>36648</t>
-  </si>
-  <si>
-    <t>Causa Raiz - BI retrabalho TT - Reunião</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Precisamos incluir no banco de dados do BI do retrabalho de Tratamento Térmico a causa raiz do retrabalho. Essa informação é crucial para usar o BI de forma integral, sem necessidade de suporte de excel paralelo. Atualmente no excel tenho o banco de dados dessa maneira: DIA MÊS MÊS EXTENSO </t>
-  </si>
-  <si>
-    <t>Gilberto José Rebelo Junior</t>
-  </si>
-  <si>
-    <t>13/02/2026</t>
+    <t>Alteração de registro de pintura</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>19909</t>
+  </si>
+  <si>
+    <t>Criar KB Genexus especifica para Registro de pinturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Visando uma melhoria no setor de pintura e uma adequação para ISO9001, o registro de pintura é hoje realizado manualmente pelo pintor, correndo assim, o risco do mesmo esquecer de preencher o documento ao final da atividade. A ideia seria inserir um registro digital, parecido com o que é </t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>25/04/2023</t>
+  </si>
+  <si>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>36206</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - API</t>
+  </si>
+  <si>
+    <t>37015</t>
+  </si>
+  <si>
+    <t>DIFA Interno e fretes - Ajuste de observação fiscal - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Nas notas de DIFA interno e DIFA nos fretes precisa ser enviado os registros de observação fiscal e ajustes, conforme exemplo da NF 186758: O campo OBSERVACAO=@CODIGO(881) será o mesmo, o que vai mudar é o campo CODIGOAJUSTEBENEFICIO Nas notas de CFOP 1.556 e 1.551 o código de ajuste será S</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>33549</t>
+  </si>
+  <si>
+    <t>Integração de sistema Logística x data book - Relatório x Registro End's</t>
+  </si>
+  <si>
+    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
+  </si>
+  <si>
+    <t>Rosivaldo Silva</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>37160</t>
+  </si>
+  <si>
+    <t>Conversão da KB comercial para Gx18</t>
+  </si>
+  <si>
+    <t>Prezados, Precisamos migrar a aplicação do comercial, atualmente na versão gx75 para a versão 18. Principais entregas: - Levantar funcionalidades usadas e necessárias para a migração - Desenhar fluxo de trabalho com aplicação web - Converter objetos Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>30069</t>
+  </si>
+  <si>
+    <t>Controle de Importação - integração financeira</t>
+  </si>
+  <si>
+    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
+  </si>
+  <si>
+    <t>11/02/2025</t>
+  </si>
+  <si>
+    <t>31836</t>
+  </si>
+  <si>
+    <t>Melhoria WMS - Conferencia e Carregamento</t>
+  </si>
+  <si>
+    <t>Boa tarde Precisamos que as etapas de Saida Deposito do WMS possam ser revertidas e editadas após o processo "finalizado". * Uma vez realizado o carregamento, que seja possível , voltar e excluir NF / itens. Sugestão: selecionar os romaneios (já vinculados a NF) e excluir, voltando os Romaneios a St</t>
+  </si>
+  <si>
+    <t>22/05/2025</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>32150</t>
+  </si>
+  <si>
+    <t>Inventario WMS - Registro de Ajuste de Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
+  </si>
+  <si>
+    <t>06/06/2025</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>34960</t>
+  </si>
+  <si>
+    <t>"Divergência no status da invoice - Precisa acessar a tela para atualizar o status"</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel, Gentileza vincular o campo do Status da Parcela do registro de cambio com o Status da Parcela da Invoice. Quando alterado para parcial ou pago no Registro de Cambio, deve ser atualizada a Invoice. Gentileza atualizar todo o histórico desde 2019 ajustando o sistema de Invoice. Exempl</t>
+  </si>
+  <si>
+    <t>29/10/2025</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>36262</t>
+  </si>
+  <si>
+    <t>Melhoria | Vinculo de Atraso na Invoice</t>
+  </si>
+  <si>
+    <t>Boa tarde, Maciel, Criar uma opção na tela da Invoice abaixo, abaixo de modal que caso o Modal ser "Aéreo" obrigar informar uma das opções abaixo: * Atraso de produção * Venda aérea * A ser cobrado do cliente Caso o Modal não for aéreo, deixar a opção bloqueada. Precisará vincular o qvd CPC389 o nov</t>
+  </si>
+  <si>
+    <t>26/01/2026</t>
+  </si>
+  <si>
+    <t>37216</t>
+  </si>
+  <si>
+    <t>Entrada de Conjuntos com qtd diferente</t>
+  </si>
+  <si>
+    <t>Boa tarde Flavio Conforme conversamos e foi ajustado pontualmente, temos a situação dois conjuntos com mesmo componente e quantidades diferentes. Abaixo os itens.</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
+    <t>37276</t>
+  </si>
+  <si>
+    <t>Melhoria | QVD do Controle da Valorização - Reunião</t>
+  </si>
+  <si>
+    <t>Conforme conversado com o Felipe, fazer avaliação de como pode ser realizado o qvd do Controle da valorização, que tem base no F e do controle de coletas.</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>37382</t>
+  </si>
+  <si>
+    <t>Ajuste nas permissões dos usuários - Gestão de Ações</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos ajustar algumas permissões dos usuários no sistema Gestão de Ações. Componente: "CADASTROS", somente Admin´s podem ter acesso. Componente: "PLANO DE AÇÃO"(Cadastro), somente os Admin´s, Grupo de trabalho, Responsável pelo plano e responsável por ações, podem acessar seus planos n</t>
+  </si>
+  <si>
+    <t>Matheus Gonçalves</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>37374</t>
+  </si>
+  <si>
+    <t>Melhoria do sistema de Cadastros</t>
+  </si>
+  <si>
+    <t>Boa tarde, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1. Filtrar apelas as unidades de medida ativas no sistema. 1. Necessário aumentar a quantidade de caracteres no campo nomenclatura. ( no mínimo 100caracteres) 1. Colocar um botão d</t>
+  </si>
+  <si>
+    <t>Vanessa Knoth</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>35956</t>
+  </si>
+  <si>
+    <t>LISTAGEM DE NORMAS POR OTF</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor criar uma listagem de todas as OTFs produzidas de 01/01/2024 até 31/12/2025 correlacionando com a coluna "Norma Para Certificados" na tela WCPP221B de cada OTF. At.te</t>
+  </si>
+  <si>
+    <t>08/01/2026</t>
+  </si>
+  <si>
+    <t>35977</t>
+  </si>
+  <si>
+    <t>Falha Sistema de Indicadores GIQ</t>
+  </si>
+  <si>
+    <t>Olá, No ano passado pedi para alterar o campo da média/acumulado para um campo editável, mas agora apareceu umas falhas no cálculo, então proponho as seguintes correções: 1) Na página de incluir as Metas do indicador, a média da meta deve ser um campo travado não editável e precisa ser calculada soz</t>
+  </si>
+  <si>
+    <t>Helena Mariana Segalla</t>
+  </si>
+  <si>
+    <t>09/01/2026</t>
+  </si>
+  <si>
+    <t>36342</t>
+  </si>
+  <si>
+    <t>Solicitação de ajuste de trava no sistema de inventário – WMS</t>
+  </si>
+  <si>
+    <t>Boa tarde! Precisamos realizar um ajuste no sistema de inventário do WMS. Atualmente, ao realizar inventário de materiais, o sistema emite uma mensagem de alerta quando existe uma pré‑lista em aberto, porém ainda permite a continuidade do processo. Já no caso de EPIs, o sistema não emite qualquer al</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>37114</t>
+  </si>
+  <si>
+    <t>sistema de cadastro de modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ao cadastrar um modelo com os mesmos que já tenha em outro cadastro, o mesmo desaparece do sistema, é necessário alterar esta formula, exemplo, hoje alterei o codigo do cliente deste modelo 1802380, o cadastro sumiu pois tem outro com o mesmo cadastro de cliente e material. Para um novo cadastro de </t>
+  </si>
+  <si>
+    <t>Fernando Beltrame</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>36502</t>
+  </si>
+  <si>
+    <t>qlik sense correção grafico 5s</t>
+  </si>
+  <si>
+    <t>qlik sense corrreção grafico 5s</t>
+  </si>
+  <si>
+    <t>Luiz Ricardo Bottin</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>37134</t>
+  </si>
+  <si>
+    <t>AJUSTES APONTAMENTO LINHA MESA REDONDA UPR</t>
+  </si>
+  <si>
+    <t>Bom dia, Iniciamos hoje (09/03/2026) os primeiros apontamentos na linha mesa redonda UPR, operador sugeriu para agilizar seu apontamento deixar as principais paradas de mais fácil acesso. Uma ideia muito inteligente que irá agilizar muito o processo de apontamento, ele não vai precisar ficar procura</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>37182</t>
+  </si>
+  <si>
+    <t>Análise</t>
+  </si>
+  <si>
+    <t>AJUSTES - EXTRAÇÃO DE DADOS APONTAMENTO LINHA MESAS REDONDAS</t>
+  </si>
+  <si>
+    <t>Bom dia, No dia 10/03/2026 iniciamos o piloto de apontamento eletrônico na linha mesas redondas, feito a extração em Excel notamos alguns pontos que precisam ser ajustados. * Coluna Y plan 1 (percentual executado) - puxando informações incorretas comparando com o que está sendo apontado no tablet. *</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>37174</t>
+  </si>
+  <si>
+    <t>Programação de ajustem APS</t>
+  </si>
+  <si>
+    <t>Boa tarde! Preparar arquivo QVD, para integração do ERP para o APS na programação da ajustagem: Local apontamento Modelo Tempo padrão Status Apontamento Nome operador Tipo operação Dúvidas a disposição! Obrigado! At.te,</t>
+  </si>
+  <si>
+    <t>Cristiano Nazário</t>
+  </si>
+  <si>
+    <t>37183</t>
+  </si>
+  <si>
+    <t>Retirada do (SIM)!</t>
+  </si>
+  <si>
+    <t>Bom dia, Por gentileza, preciso retirar a confirmação do (SIM), tanto na coleta quando na entrega. At.te</t>
+  </si>
+  <si>
+    <t>Johnny José Rocha</t>
+  </si>
+  <si>
+    <t>37170</t>
+  </si>
+  <si>
+    <t>Sistema de apontamento - pó de ferro</t>
+  </si>
+  <si>
+    <t>Boa tarde, preciso que seja feita algumas alterações no sistema de apontamento dos tablets. · Pesquisa de sequência no sistema do Tablet - com objetivo de verificar quando, por quem e como a peça foi cortada. · Aba movimentação de peças: não está sendo feita a movimentação de peça por mais que ela e</t>
+  </si>
+  <si>
+    <t>Amanda Vitoria Aroeira Marinho</t>
+  </si>
+  <si>
+    <t>37361</t>
+  </si>
+  <si>
+    <t>Base Histórica da Data de Reconhecimento  de Receita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
+  </si>
+  <si>
+    <t>37330</t>
+  </si>
+  <si>
+    <t>MELHORIAS NO APONTAEMNTO LINHA FASE 4 - UPR</t>
+  </si>
+  <si>
+    <t>Boa tarde, Estamos enfrentando uma dificuldade em dividir tempos na linha fase 4 que se encontra hoje em teste. Precisamos que o tempo da peça (sequência) que se encontra finalizada (100% indicado pelo operador) com retoques marcadas pela inspeção próximo a troca de turno, seja somado ao apontamento</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>37365</t>
+  </si>
+  <si>
+    <t>Pdf relacionad a dados testes de força.</t>
+  </si>
+  <si>
+    <t>Boa tarde! Solicito inserção de um pdf para visualizar os dados de teste de força na plataforma de ergonomia, igual aos pdf's que aparece na ficha de queixa. Desde já agradeço. At.te</t>
+  </si>
+  <si>
+    <t>Joice Kroening</t>
+  </si>
+  <si>
+    <t>37294</t>
+  </si>
+  <si>
+    <t>WMS - Abertura de chamado sem identificação</t>
+  </si>
+  <si>
+    <t>Bom dia Maciel, gentileza criar regra para abertura de chamado, para que seja obrigatório o preenchimento do código ou do contentor, pois esta gerando OM sem informação.</t>
+  </si>
+  <si>
+    <t>Rafael De Souza</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>37282</t>
+  </si>
+  <si>
+    <t>Inclusão do campo "Romaneio" na declaração de recebimento</t>
+  </si>
+  <si>
+    <t>Boa tarde! solicito a inclusão de busca por Romaneio na declaração de recebimento, pois nesses casos não conseguimos buscar para gerar a declaração.</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>37288</t>
+  </si>
+  <si>
+    <t>melhoria no sistema de inventário das embalagens</t>
+  </si>
+  <si>
+    <t>Bom dia! Com o aval do Rafael, solicito uma melhoria no sistema de inventário das embalagens (caixas Magayver). Atualmente, o sistema considera apenas as embalagens contadas fisicamente. Porém, existe a possibilidade de haver saldo no sistema mesmo quando a embalagem não existe fisicamente. Diante d</t>
+  </si>
+  <si>
+    <t>37354</t>
+  </si>
+  <si>
+    <t>saldo negativo EPI</t>
+  </si>
+  <si>
+    <t>Bom dia! Identificamos um problema de saldo negativo no ERP. Apesar disso, o sistema de pré-lista ainda está permitindo requisições e baixas, possivelmente porque há saldo disponível no estoque intermediário. Lembro que já havíamos solicitado a criação de uma trava na pré-lista para impedir requisiç</t>
+  </si>
+  <si>
+    <t>37255</t>
+  </si>
+  <si>
+    <t>Altona || Cadastro P&amp;D</t>
+  </si>
+  <si>
+    <t>Bom dia, Sandro! Solicito algumas melhorias na tela de cadastro do P&amp;D (imagem abaixo). 1) Liberar o acesso desse sistema para os funcionários abaixo: Paula Rosa Grando - 142830 Jeferson Borges - 131580 2) Incrementar automaticamente o número do projeto e sugerir um novo, mas não bloquear esse campo</t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
   </si>
   <si>
     <t>27/04/2026</t>
   </si>
   <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>37006</t>
-  </si>
-  <si>
-    <t>Qlik - Inclusão de campos novos qvd</t>
-  </si>
-  <si>
-    <t>Boa tarde Gentileza atualizar os qvds conforme abaixo: * Atualizar o qvd CPC389 com o campo novo abaixo "Motivo Modal Aéreo": [lib://Qlik Files - Root/QVD/EXTRACAO/CPC389.qvd] * Atualizar o qvd CTEEMIT com o campo novo abaixo "Data de Entrega" e "Frete dedicadop/ atraso": [lib://Qlik Files - Root/QV</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>03/03/2026</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>36467</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Sitema retrabalho ajustagem com erro</t>
-  </si>
-  <si>
-    <t>Boa tarde! Enviando para o Email correto. Gentileza considerar o e-mail abaixo. Atenciosamente, De: Fernanda da Costa Rodrigues Enviada em: quarta-feira, 4 de fevereiro de 2026 14:25 Para: 'Suporte Altona' Cc: Edson João Hammermeister ; Lucas José Sebold Assunto: RES: Resolvido: Sitema retrabalho aj</t>
-  </si>
-  <si>
-    <t>Fernanda da Costa Rodrigues</t>
-  </si>
-  <si>
-    <t>04/02/2026</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>36233</t>
-  </si>
-  <si>
-    <t>Automatizar apontamento dos mantenedores</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito um chamado para fazer automatização dos dados Hora ponto X Horas apontadas, com uma média mínima de 75% de apontamento. E ao mesmo tempo uma análise de total de ordens baixadas, ordens pendentes e somatório das ordens (baixadas/pendentes). Em anexos, está um modelo que estamos us</t>
-  </si>
-  <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
-    <t>36454</t>
-  </si>
-  <si>
-    <t>Inclusão de Corrida/forno/ano</t>
-  </si>
-  <si>
-    <t>Bom dia, Seria possível incluir na Tabela de linhas de produção no QlikSense a corrida, forno e ano de aciaria, isso facilita na analise de dados para o retrabalho de tratamento térmico, já que temos que tratar todas por corrida, e a reprova desses ensaios causa o retrabalhar todas as peças da corri</t>
-  </si>
-  <si>
-    <t>Eduardo Basso Pinto</t>
-  </si>
-  <si>
-    <t>36863</t>
-  </si>
-  <si>
-    <t>Aplicação QlikSense com dados do MESS</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito um chamado para que a aplicação do QlikSense comece a utilizar os dados do MESS para que possamos analisar os dados lançados. Aba da aplicação em anexo.</t>
-  </si>
-  <si>
-    <t>25/02/2026</t>
-  </si>
-  <si>
-    <t>36299</t>
-  </si>
-  <si>
-    <t>Calcular indicadores através dos dados do CRP</t>
-  </si>
-  <si>
-    <t>Bom dia, Quero solicitar um chamado para que os cálculos do MTTR, MDT, MTBF e Disponibilidade de Máquina sejam calculados através dados Usinagem IROG - Operações de manutenções, pois são atualizados diariamente. E através disto criar um compartimento deles para que fiquem visíveis na mesma aba confo</t>
-  </si>
-  <si>
-    <t>28/01/2026</t>
-  </si>
-  <si>
-    <t>35467</t>
-  </si>
-  <si>
-    <t>Alterar Cálculo do Custo de SUCATA RETORNO</t>
-  </si>
-  <si>
-    <t>Bom dia a todos! O processo de controle dos estoques de SUCATA RETORNO está em aprimoramento, para tanto, é preciso implementar alterações de sistema válidas a partir de 01/01/2026: Segue forma de cálculo: 1. Entrada em estoque a partir Corte de Canal. * Peso a ser considerado para Entrada, peso ali</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>27/11/2025</t>
-  </si>
-  <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>23773</t>
-  </si>
-  <si>
-    <t>Problema</t>
-  </si>
-  <si>
-    <t>Registro de moldagem USE/ULE</t>
-  </si>
-  <si>
-    <t>Bom dia, Estamos tendo inconsistência nos registros de Moldagem USE/ULE, acontece às vezes do registro ser finalizado e a movimentação não ocorrer. Ocorre tanto na ULE como na USE. Exemplos abaixo: Duvidas entrar em contato. Att.</t>
-  </si>
-  <si>
-    <t>Darlan Pressi</t>
-  </si>
-  <si>
-    <t>19/12/2023</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>35426</t>
-  </si>
-  <si>
-    <t>Ajustar quem pode movimentar</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor revisar as permissões dos setores de amostra conforme abaixo. Esse setores são apenas para os membros da minha equipe, pois os demais não tem conhecimento para poder movimentá-los. Setor 596 - LIBERAÇÃO DE AMOSTRAS Remover 144773 e 145261 Setor 597 - FECHAMENTO DE AMOSTRAS Remover 1</t>
-  </si>
-  <si>
-    <t>Paula Rosa M. Grando</t>
-  </si>
-  <si>
-    <t>25/11/2025</t>
-  </si>
-  <si>
-    <t>36724</t>
-  </si>
-  <si>
-    <t>Alteração de registro de pintura</t>
-  </si>
-  <si>
-    <t>Sistema de registro de pintura: Teria como o Log aparecer de uma forma parecida com essa descrição? ( Cadastro de quem alterou), (Descrição do que foi alterado Ex. Alterado medição da camada Top Coat com tolerância: Min.: ........., Max.: .........., Medição anterior: ............, Alterado para: ..</t>
-  </si>
-  <si>
-    <t>Lucas Sebold Movidesk</t>
-  </si>
-  <si>
-    <t>18/02/2026</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>19909</t>
-  </si>
-  <si>
-    <t>Criar KB Genexus especifica para Registro de pinturas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Visando uma melhoria no setor de pintura e uma adequação para ISO9001, o registro de pintura é hoje realizado manualmente pelo pintor, correndo assim, o risco do mesmo esquecer de preencher o documento ao final da atividade. A ideia seria inserir um registro digital, parecido com o que é </t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>25/04/2023</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>36206</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - API</t>
-  </si>
-  <si>
-    <t>37015</t>
-  </si>
-  <si>
-    <t>DIFA Interno e fretes - Ajuste de observação fiscal - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Nas notas de DIFA interno e DIFA nos fretes precisa ser enviado os registros de observação fiscal e ajustes, conforme exemplo da NF 186758: O campo OBSERVACAO=@CODIGO(881) será o mesmo, o que vai mudar é o campo CODIGOAJUSTEBENEFICIO Nas notas de CFOP 1.556 e 1.551 o código de ajuste será S</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>04/03/2026</t>
-  </si>
-  <si>
-    <t>33549</t>
-  </si>
-  <si>
-    <t>Integração de sistema Logística x data book - Relatório x Registro End's</t>
-  </si>
-  <si>
-    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
-  </si>
-  <si>
-    <t>Rosivaldo Silva</t>
-  </si>
-  <si>
-    <t>18/08/2025</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>37160</t>
-  </si>
-  <si>
-    <t>Conversão da KB comercial para Gx18</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos migrar a aplicação do comercial, atualmente na versão gx75 para a versão 18. Principais entregas: - Levantar funcionalidades usadas e necessárias para a migração - Desenhar fluxo de trabalho com aplicação web - Converter objetos Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>30069</t>
-  </si>
-  <si>
-    <t>Controle de Importação - integração financeira</t>
-  </si>
-  <si>
-    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
-  </si>
-  <si>
-    <t>11/02/2025</t>
-  </si>
-  <si>
-    <t>31836</t>
-  </si>
-  <si>
-    <t>Melhoria WMS - Conferencia e Carregamento</t>
-  </si>
-  <si>
-    <t>Boa tarde Precisamos que as etapas de Saida Deposito do WMS possam ser revertidas e editadas após o processo "finalizado". * Uma vez realizado o carregamento, que seja possível , voltar e excluir NF / itens. Sugestão: selecionar os romaneios (já vinculados a NF) e excluir, voltando os Romaneios a St</t>
-  </si>
-  <si>
-    <t>22/05/2025</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>32150</t>
-  </si>
-  <si>
-    <t>Inventario WMS - Registro de Ajuste de Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
-  </si>
-  <si>
-    <t>06/06/2025</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>34960</t>
-  </si>
-  <si>
-    <t>"Divergência no status da invoice - Precisa acessar a tela para atualizar o status"</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel, Gentileza vincular o campo do Status da Parcela do registro de cambio com o Status da Parcela da Invoice. Quando alterado para parcial ou pago no Registro de Cambio, deve ser atualizada a Invoice. Gentileza atualizar todo o histórico desde 2019 ajustando o sistema de Invoice. Exempl</t>
-  </si>
-  <si>
-    <t>29/10/2025</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>36262</t>
-  </si>
-  <si>
-    <t>Melhoria | Vinculo de Atraso na Invoice</t>
-  </si>
-  <si>
-    <t>Boa tarde, Maciel, Criar uma opção na tela da Invoice abaixo, abaixo de modal que caso o Modal ser "Aéreo" obrigar informar uma das opções abaixo: * Atraso de produção * Venda aérea * A ser cobrado do cliente Caso o Modal não for aéreo, deixar a opção bloqueada. Precisará vincular o qvd CPC389 o nov</t>
-  </si>
-  <si>
-    <t>26/01/2026</t>
-  </si>
-  <si>
-    <t>37216</t>
-  </si>
-  <si>
-    <t>Entrada de Conjuntos com qtd diferente</t>
-  </si>
-  <si>
-    <t>Boa tarde Flavio Conforme conversamos e foi ajustado pontualmente, temos a situação dois conjuntos com mesmo componente e quantidades diferentes. Abaixo os itens.</t>
-  </si>
-  <si>
-    <t>12/03/2026</t>
-  </si>
-  <si>
-    <t>37276</t>
-  </si>
-  <si>
-    <t>Melhoria | QVD do Controle da Valorização - Reunião</t>
-  </si>
-  <si>
-    <t>Conforme conversado com o Felipe, fazer avaliação de como pode ser realizado o qvd do Controle da valorização, que tem base no F e do controle de coletas.</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>37382</t>
-  </si>
-  <si>
-    <t>Ajuste nas permissões dos usuários - Gestão de Ações</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos ajustar algumas permissões dos usuários no sistema Gestão de Ações. Componente: "CADASTROS", somente Admin´s podem ter acesso. Componente: "PLANO DE AÇÃO"(Cadastro), somente os Admin´s, Grupo de trabalho, Responsável pelo plano e responsável por ações, podem acessar seus planos n</t>
-  </si>
-  <si>
-    <t>Matheus Gonçalves</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>37374</t>
-  </si>
-  <si>
-    <t>Melhoria do sistema de Cadastros</t>
-  </si>
-  <si>
-    <t>Boa tarde, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1. Filtrar apelas as unidades de medida ativas no sistema. 1. Necessário aumentar a quantidade de caracteres no campo nomenclatura. ( no mínimo 100caracteres) 1. Colocar um botão d</t>
-  </si>
-  <si>
-    <t>Vanessa Knoth</t>
-  </si>
-  <si>
-    <t>19/03/2026</t>
-  </si>
-  <si>
-    <t>35956</t>
-  </si>
-  <si>
-    <t>LISTAGEM DE NORMAS POR OTF</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor criar uma listagem de todas as OTFs produzidas de 01/01/2024 até 31/12/2025 correlacionando com a coluna "Norma Para Certificados" na tela WCPP221B de cada OTF. At.te</t>
-  </si>
-  <si>
-    <t>08/01/2026</t>
-  </si>
-  <si>
-    <t>35977</t>
-  </si>
-  <si>
-    <t>Falha Sistema de Indicadores GIQ</t>
-  </si>
-  <si>
-    <t>Olá, No ano passado pedi para alterar o campo da média/acumulado para um campo editável, mas agora apareceu umas falhas no cálculo, então proponho as seguintes correções: 1) Na página de incluir as Metas do indicador, a média da meta deve ser um campo travado não editável e precisa ser calculada soz</t>
-  </si>
-  <si>
-    <t>Helena Mariana Segalla</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>36342</t>
-  </si>
-  <si>
-    <t>Solicitação de ajuste de trava no sistema de inventário – WMS</t>
-  </si>
-  <si>
-    <t>Boa tarde! Precisamos realizar um ajuste no sistema de inventário do WMS. Atualmente, ao realizar inventário de materiais, o sistema emite uma mensagem de alerta quando existe uma pré‑lista em aberto, porém ainda permite a continuidade do processo. Já no caso de EPIs, o sistema não emite qualquer al</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>37114</t>
-  </si>
-  <si>
-    <t>sistema de cadastro de modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ao cadastrar um modelo com os mesmos que já tenha em outro cadastro, o mesmo desaparece do sistema, é necessário alterar esta formula, exemplo, hoje alterei o codigo do cliente deste modelo 1802380, o cadastro sumiu pois tem outro com o mesmo cadastro de cliente e material. Para um novo cadastro de </t>
-  </si>
-  <si>
-    <t>Fernando Beltrame</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>36502</t>
-  </si>
-  <si>
-    <t>qlik sense correção grafico 5s</t>
-  </si>
-  <si>
-    <t>qlik sense corrreção grafico 5s</t>
-  </si>
-  <si>
-    <t>Luiz Ricardo Bottin</t>
-  </si>
-  <si>
-    <t>05/02/2026</t>
-  </si>
-  <si>
-    <t>37134</t>
-  </si>
-  <si>
-    <t>AJUSTES APONTAMENTO LINHA MESA REDONDA UPR</t>
-  </si>
-  <si>
-    <t>Bom dia, Iniciamos hoje (09/03/2026) os primeiros apontamentos na linha mesa redonda UPR, operador sugeriu para agilizar seu apontamento deixar as principais paradas de mais fácil acesso. Uma ideia muito inteligente que irá agilizar muito o processo de apontamento, ele não vai precisar ficar procura</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>37182</t>
-  </si>
-  <si>
-    <t>Análise</t>
-  </si>
-  <si>
-    <t>AJUSTES - EXTRAÇÃO DE DADOS APONTAMENTO LINHA MESAS REDONDAS</t>
-  </si>
-  <si>
-    <t>Bom dia, No dia 10/03/2026 iniciamos o piloto de apontamento eletrônico na linha mesas redondas, feito a extração em Excel notamos alguns pontos que precisam ser ajustados. * Coluna Y plan 1 (percentual executado) - puxando informações incorretas comparando com o que está sendo apontado no tablet. *</t>
-  </si>
-  <si>
-    <t>11/03/2026</t>
-  </si>
-  <si>
-    <t>37174</t>
-  </si>
-  <si>
-    <t>Programação de ajustem APS</t>
-  </si>
-  <si>
-    <t>Boa tarde! Preparar arquivo QVD, para integração do ERP para o APS na programação da ajustagem: Local apontamento Modelo Tempo padrão Status Apontamento Nome operador Tipo operação Dúvidas a disposição! Obrigado! At.te,</t>
-  </si>
-  <si>
-    <t>Cristiano Nazário</t>
-  </si>
-  <si>
-    <t>37183</t>
-  </si>
-  <si>
-    <t>Retirada do (SIM)!</t>
-  </si>
-  <si>
-    <t>Bom dia, Por gentileza, preciso retirar a confirmação do (SIM), tanto na coleta quando na entrega. At.te</t>
-  </si>
-  <si>
-    <t>Johnny José Rocha</t>
-  </si>
-  <si>
-    <t>37170</t>
-  </si>
-  <si>
-    <t>Sistema de apontamento - pó de ferro</t>
-  </si>
-  <si>
-    <t>Boa tarde, preciso que seja feita algumas alterações no sistema de apontamento dos tablets. · Pesquisa de sequência no sistema do Tablet - com objetivo de verificar quando, por quem e como a peça foi cortada. · Aba movimentação de peças: não está sendo feita a movimentação de peça por mais que ela e</t>
-  </si>
-  <si>
-    <t>Amanda Vitoria Aroeira Marinho</t>
-  </si>
-  <si>
-    <t>37361</t>
-  </si>
-  <si>
-    <t>Base Histórica da Data de Reconhecimento  de Receita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
-  </si>
-  <si>
-    <t>37330</t>
-  </si>
-  <si>
-    <t>MELHORIAS NO APONTAEMNTO LINHA FASE 4 - UPR</t>
-  </si>
-  <si>
-    <t>Boa tarde, Estamos enfrentando uma dificuldade em dividir tempos na linha fase 4 que se encontra hoje em teste. Precisamos que o tempo da peça (sequência) que se encontra finalizada (100% indicado pelo operador) com retoques marcadas pela inspeção próximo a troca de turno, seja somado ao apontamento</t>
-  </si>
-  <si>
-    <t>18/03/2026</t>
-  </si>
-  <si>
-    <t>37365</t>
-  </si>
-  <si>
-    <t>Pdf relacionad a dados testes de força.</t>
-  </si>
-  <si>
-    <t>Boa tarde! Solicito inserção de um pdf para visualizar os dados de teste de força na plataforma de ergonomia, igual aos pdf's que aparece na ficha de queixa. Desde já agradeço. At.te</t>
-  </si>
-  <si>
-    <t>Joice Kroening</t>
-  </si>
-  <si>
-    <t>37294</t>
-  </si>
-  <si>
-    <t>WMS - Abertura de chamado sem identificação</t>
-  </si>
-  <si>
-    <t>Bom dia Maciel, gentileza criar regra para abertura de chamado, para que seja obrigatório o preenchimento do código ou do contentor, pois esta gerando OM sem informação.</t>
-  </si>
-  <si>
-    <t>Rafael De Souza</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
-  </si>
-  <si>
-    <t>37282</t>
-  </si>
-  <si>
-    <t>Inclusão do campo "Romaneio" na declaração de recebimento</t>
-  </si>
-  <si>
-    <t>Boa tarde! solicito a inclusão de busca por Romaneio na declaração de recebimento, pois nesses casos não conseguimos buscar para gerar a declaração.</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>37288</t>
-  </si>
-  <si>
-    <t>melhoria no sistema de inventário das embalagens</t>
-  </si>
-  <si>
-    <t>Bom dia! Com o aval do Rafael, solicito uma melhoria no sistema de inventário das embalagens (caixas Magayver). Atualmente, o sistema considera apenas as embalagens contadas fisicamente. Porém, existe a possibilidade de haver saldo no sistema mesmo quando a embalagem não existe fisicamente. Diante d</t>
-  </si>
-  <si>
-    <t>23/04/2026</t>
-  </si>
-  <si>
-    <t>37354</t>
-  </si>
-  <si>
-    <t>saldo negativo EPI</t>
-  </si>
-  <si>
-    <t>Bom dia! Identificamos um problema de saldo negativo no ERP. Apesar disso, o sistema de pré-lista ainda está permitindo requisições e baixas, possivelmente porque há saldo disponível no estoque intermediário. Lembro que já havíamos solicitado a criação de uma trava na pré-lista para impedir requisiç</t>
-  </si>
-  <si>
-    <t>37255</t>
-  </si>
-  <si>
-    <t>Altona || Cadastro P&amp;D</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Solicito algumas melhorias na tela de cadastro do P&amp;D (imagem abaixo). 1) Liberar o acesso desse sistema para os funcionários abaixo: Paula Rosa Grando - 142830 Jeferson Borges - 131580 2) Incrementar automaticamente o número do projeto e sugerir um novo, mas não bloquear esse campo</t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>28/04/2026</t>
-  </si>
-  <si>
     <t>37368</t>
   </si>
   <si>
@@ -873,6 +861,9 @@
     <t>Report técnico - Acompanhamento</t>
   </si>
   <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
     <t>36213</t>
   </si>
   <si>
@@ -1089,15 +1080,6 @@
     <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
   </si>
   <si>
-    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
-  </si>
-  <si>
-    <t>Alini Ferreira Ganda</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
     <t>35738</t>
   </si>
   <si>
@@ -1125,6 +1107,9 @@
     <t>Boa tarde, Hoje (20/03/26 ) foi criado as operações jato dirigido para cadastrarmos os tempos na CPP para rateio de tempo Qlik. Precisamos que esse rateio seja retroativo. No apontamento eletrônico o estado da peça era somente apontado para informação e não apontado sua real operação. Precisamos que</t>
   </si>
   <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
     <t>36335</t>
   </si>
   <si>
@@ -1194,7 +1179,7 @@
     <t>@Maciel, Poderia remover o campo "Qty.:" dos componentes quando for oferta de conjunto? Tanto de Brasil quanto de exportação, pois essa quantidade é o número de placas no modelo, não tem necessidade de aparecer na oferta para o cliente. Obrigada!!</t>
   </si>
   <si>
-    <t>06/05/2026</t>
+    <t>05/05/2026</t>
   </si>
   <si>
     <t>36677</t>
@@ -2195,7 +2180,7 @@
         <v>80</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -2204,12 +2189,12 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
@@ -2218,25 +2203,25 @@
         <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>79</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>42</v>
@@ -2245,15 +2230,15 @@
         <v>35</v>
       </c>
       <c r="M12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
@@ -2265,22 +2250,22 @@
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>24</v>
@@ -2292,56 +2277,56 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>97</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -2353,60 +2338,60 @@
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>22</v>
@@ -2415,10 +2400,10 @@
         <v>33</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>26</v>
@@ -2429,28 +2414,28 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>22</v>
@@ -2459,7 +2444,7 @@
         <v>33</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -2473,7 +2458,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -2485,22 +2470,22 @@
         <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>42</v>
@@ -2517,7 +2502,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -2529,39 +2514,39 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N19" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -2573,28 +2558,28 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>43</v>
@@ -2605,7 +2590,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -2617,10 +2602,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -2632,16 +2617,16 @@
         <v>79</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>36</v>
@@ -2649,7 +2634,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2661,10 +2646,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>31</v>
@@ -2676,13 +2661,13 @@
         <v>79</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>43</v>
@@ -2693,7 +2678,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2705,10 +2690,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>31</v>
@@ -2720,10 +2705,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>35</v>
@@ -2732,12 +2717,12 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2749,10 +2734,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>31</v>
@@ -2764,7 +2749,7 @@
         <v>79</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>34</v>
@@ -2776,12 +2761,12 @@
         <v>49</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2793,10 +2778,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -2808,7 +2793,7 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>24</v>
@@ -2817,15 +2802,15 @@
         <v>25</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2837,10 +2822,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -2852,7 +2837,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2869,7 +2854,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2881,10 +2866,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
@@ -2896,7 +2881,7 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>24</v>
@@ -2913,7 +2898,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2925,10 +2910,10 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2940,7 +2925,7 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>24</v>
@@ -2949,7 +2934,7 @@
         <v>25</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>50</v>
@@ -2957,7 +2942,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2969,22 +2954,22 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>24</v>
@@ -2993,7 +2978,7 @@
         <v>25</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>50</v>
@@ -3001,7 +2986,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -3013,22 +2998,22 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>24</v>
@@ -3037,7 +3022,7 @@
         <v>25</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>50</v>
@@ -3045,7 +3030,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -3057,10 +3042,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -3072,7 +3057,7 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>24</v>
@@ -3089,7 +3074,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -3101,22 +3086,22 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>24</v>
@@ -3133,7 +3118,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -3145,31 +3130,31 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>36</v>
@@ -3177,7 +3162,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -3189,22 +3174,22 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>24</v>
@@ -3221,7 +3206,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -3233,22 +3218,22 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>24</v>
@@ -3265,7 +3250,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -3277,22 +3262,22 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>24</v>
@@ -3309,34 +3294,34 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>42</v>
@@ -3353,7 +3338,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -3365,22 +3350,22 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>24</v>
@@ -3397,7 +3382,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -3409,22 +3394,22 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>24</v>
@@ -3441,7 +3426,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -3453,22 +3438,22 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>24</v>
@@ -3485,7 +3470,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -3497,10 +3482,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3512,16 +3497,16 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>50</v>
@@ -3529,7 +3514,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3541,22 +3526,22 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>34</v>
@@ -3565,7 +3550,7 @@
         <v>25</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>50</v>
@@ -3573,7 +3558,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3585,22 +3570,22 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>24</v>
@@ -3609,7 +3594,7 @@
         <v>25</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>50</v>
@@ -3617,7 +3602,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3629,22 +3614,22 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>24</v>
@@ -3653,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>50</v>
@@ -3661,7 +3646,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3673,31 +3658,31 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>50</v>
@@ -3705,7 +3690,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3717,31 +3702,31 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>247</v>
+        <v>42</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>50</v>
@@ -3749,7 +3734,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3758,34 +3743,34 @@
         <v>16</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>50</v>
@@ -3793,7 +3778,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3805,31 +3790,31 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>50</v>
@@ -3837,7 +3822,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3849,22 +3834,22 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>24</v>
@@ -3873,7 +3858,7 @@
         <v>25</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>50</v>
@@ -3881,7 +3866,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3893,22 +3878,22 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>24</v>
@@ -3917,7 +3902,7 @@
         <v>25</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>50</v>
@@ -3925,7 +3910,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3937,22 +3922,22 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>24</v>
@@ -3961,7 +3946,7 @@
         <v>25</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>50</v>
@@ -3969,37 +3954,37 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -4008,12 +3993,12 @@
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -4025,10 +4010,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -4057,7 +4042,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -4069,10 +4054,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>31</v>
@@ -4084,7 +4069,7 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>34</v>
@@ -4093,15 +4078,15 @@
         <v>25</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -4113,22 +4098,22 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>24</v>
@@ -4137,7 +4122,7 @@
         <v>25</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>36</v>
@@ -4145,7 +4130,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -4157,22 +4142,22 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>24</v>
@@ -4181,7 +4166,7 @@
         <v>25</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>36</v>
@@ -4189,7 +4174,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -4198,25 +4183,25 @@
         <v>16</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>34</v>
@@ -4228,12 +4213,12 @@
         <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -4245,16 +4230,16 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>22</v>
@@ -4277,7 +4262,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -4289,39 +4274,39 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>49</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -4333,22 +4318,22 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>24</v>
@@ -4365,7 +4350,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -4377,22 +4362,22 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>24</v>
@@ -4401,7 +4386,7 @@
         <v>25</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>27</v>
@@ -4409,7 +4394,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -4421,25 +4406,25 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>25</v>
@@ -4448,12 +4433,12 @@
         <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4462,28 +4447,28 @@
         <v>16</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>25</v>
@@ -4492,12 +4477,12 @@
         <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4509,25 +4494,25 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>25</v>
@@ -4536,12 +4521,12 @@
         <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4553,25 +4538,25 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>25</v>
@@ -4580,12 +4565,12 @@
         <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4597,25 +4582,25 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4624,12 +4609,12 @@
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4641,25 +4626,25 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4668,12 +4653,12 @@
         <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4685,25 +4670,25 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>25</v>
@@ -4712,12 +4697,12 @@
         <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4729,25 +4714,25 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
@@ -4756,12 +4741,12 @@
         <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4773,25 +4758,25 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>25</v>
@@ -4800,12 +4785,12 @@
         <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4817,22 +4802,22 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>24</v>
@@ -4844,12 +4829,12 @@
         <v>43</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4861,28 +4846,28 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>43</v>
@@ -4893,7 +4878,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4905,22 +4890,22 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>24</v>
@@ -4937,37 +4922,37 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>25</v>
@@ -4976,12 +4961,12 @@
         <v>49</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4993,25 +4978,25 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>25</v>
@@ -5020,12 +5005,12 @@
         <v>49</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -5037,22 +5022,22 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>34</v>
@@ -5069,7 +5054,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -5081,28 +5066,28 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>247</v>
+        <v>42</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>49</v>
@@ -5113,7 +5098,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -5125,10 +5110,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -5140,10 +5125,10 @@
         <v>79</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -5152,12 +5137,12 @@
         <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -5169,22 +5154,22 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>79</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>34</v>
@@ -5193,15 +5178,15 @@
         <v>25</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -5213,10 +5198,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -5228,24 +5213,24 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>42</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -5254,42 +5239,42 @@
         <v>16</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>359</v>
+        <v>96</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>360</v>
+        <v>96</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -5301,10 +5286,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>31</v>
@@ -5316,7 +5301,7 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>24</v>
@@ -5325,45 +5310,45 @@
         <v>25</v>
       </c>
       <c r="M82" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N82" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="N82" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>25</v>
@@ -5372,12 +5357,12 @@
         <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -5389,31 +5374,31 @@
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>34</v>
+        <v>364</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>50</v>
@@ -5421,7 +5406,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -5433,31 +5418,31 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>36</v>
@@ -5465,7 +5450,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5477,31 +5462,31 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>34</v>
+        <v>364</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>50</v>
@@ -5509,7 +5494,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5521,22 +5506,22 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>24</v>
@@ -5548,39 +5533,39 @@
         <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>34</v>
@@ -5597,34 +5582,34 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>34</v>
@@ -5641,34 +5626,34 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>34</v>
@@ -5685,34 +5670,34 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="F91" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>34</v>
@@ -5729,7 +5714,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5738,42 +5723,42 @@
         <v>16</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -5785,28 +5770,28 @@
         <v>17</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>34</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M93" s="2" t="s">
         <v>43</v>
@@ -5817,7 +5802,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5829,31 +5814,31 @@
         <v>17</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>79</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>50</v>
@@ -5861,7 +5846,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5870,25 +5855,25 @@
         <v>52</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>24</v>
@@ -5897,7 +5882,7 @@
         <v>25</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>27</v>
@@ -5905,7 +5890,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -5914,25 +5899,25 @@
         <v>16</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>398</v>
+        <v>282</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>34</v>
@@ -5941,10 +5926,10 @@
         <v>25</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -5960,23 +5945,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5984,16 +5969,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6012,7 +5997,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6033,7 +6018,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6064,12 +6049,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B2">
         <v>95</v>
@@ -6093,25 +6078,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6128,13 +6113,13 @@
         <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6149,7 +6134,7 @@
         <v>49</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -6166,13 +6151,13 @@
         <v>36</v>
       </c>
       <c r="J11" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="K11">
         <v>95</v>
       </c>
       <c r="M11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N11">
         <v>8</v>
@@ -6181,12 +6166,12 @@
         <v>43</v>
       </c>
       <c r="Q11">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -6198,33 +6183,33 @@
         <v>59</v>
       </c>
       <c r="M12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N12">
         <v>3</v>
       </c>
       <c r="P12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q12">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N13">
         <v>7</v>
@@ -6233,18 +6218,18 @@
         <v>26</v>
       </c>
       <c r="Q13">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6266,7 +6251,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6274,7 +6259,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6282,7 +6267,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -6293,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6301,133 +6286,133 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>336</v>
+        <v>135</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>337</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>138</v>
+        <v>333</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>139</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
@@ -6436,7 +6421,7 @@
         <v>332</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2026-10.xlsx
+++ b/utils/monday_sprint_sprint_2026-10.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="400">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -159,6 +159,9 @@
     <t>37006</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Qlik - Inclusão de campos novos qvd</t>
   </si>
   <si>
@@ -189,15 +192,15 @@
     <t>Homologação</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
     <t>36233</t>
   </si>
   <si>
+    <t>Mecânica</t>
+  </si>
+  <si>
     <t>Automatizar apontamento dos mantenedores</t>
   </si>
   <si>
@@ -210,6 +213,9 @@
     <t>36454</t>
   </si>
   <si>
+    <t>Fundição</t>
+  </si>
+  <si>
     <t>Inclusão de Corrida/forno/ano</t>
   </si>
   <si>
@@ -246,6 +252,9 @@
     <t>35467</t>
   </si>
   <si>
+    <t>Controladoria</t>
+  </si>
+  <si>
     <t>Alterar Cálculo do Custo de SUCATA RETORNO</t>
   </si>
   <si>
@@ -285,7 +294,7 @@
     <t>Paula Rosa M. Grando</t>
   </si>
   <si>
-    <t>36724</t>
+    <t>11468514039</t>
   </si>
   <si>
     <t>Categoria não informada</t>
@@ -300,864 +309,888 @@
     <t>Equipe não informada</t>
   </si>
   <si>
+    <t>22/03/2026</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>11468523088</t>
+  </si>
+  <si>
+    <t>Criar KB Genexus especifica para Registro de pinturas</t>
+  </si>
+  <si>
+    <t>36206</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - API</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>37015</t>
+  </si>
+  <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
+    <t>DIFA Interno e fretes - Ajuste de observação fiscal - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Nas notas de DIFA interno e DIFA nos fretes precisa ser enviado os registros de observação fiscal e ajustes, conforme exemplo da NF 186758: O campo OBSERVACAO=@CODIGO(881) será o mesmo, o que vai mudar é o campo CODIGOAJUSTEBENEFICIO Nas notas de CFOP 1.556 e 1.551 o código de ajuste será S</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>33549</t>
+  </si>
+  <si>
+    <t>Integração de sistema Logística x data book - Relatório x Registro End's</t>
+  </si>
+  <si>
+    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
+  </si>
+  <si>
+    <t>Rosivaldo Silva</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>37160</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>Conversão da KB comercial para Gx18</t>
+  </si>
+  <si>
+    <t>Prezados, Precisamos migrar a aplicação do comercial, atualmente na versão gx75 para a versão 18. Principais entregas: - Levantar funcionalidades usadas e necessárias para a migração - Desenhar fluxo de trabalho com aplicação web - Converter objetos Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>04/04/2026</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>30069</t>
+  </si>
+  <si>
+    <t>Controle de Importação - integração financeira</t>
+  </si>
+  <si>
+    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
+  </si>
+  <si>
+    <t>11559311646</t>
+  </si>
+  <si>
+    <t>Melhoria WMS - Conferencia e Carregamento</t>
+  </si>
+  <si>
+    <t>32150</t>
+  </si>
+  <si>
+    <t>Inventario WMS - Registro de Ajuste de Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
+  </si>
+  <si>
+    <t>34960</t>
+  </si>
+  <si>
+    <t>"Divergência no status da invoice - Precisa acessar a tela para atualizar o status"</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel, Gentileza vincular o campo do Status da Parcela do registro de cambio com o Status da Parcela da Invoice. Quando alterado para parcial ou pago no Registro de Cambio, deve ser atualizada a Invoice. Gentileza atualizar todo o histórico desde 2019 ajustando o sistema de Invoice. Exempl</t>
+  </si>
+  <si>
+    <t>36262</t>
+  </si>
+  <si>
+    <t>Melhoria | Vinculo de Atraso na Invoice</t>
+  </si>
+  <si>
+    <t>Boa tarde, Maciel, Criar uma opção na tela da Invoice abaixo, abaixo de modal que caso o Modal ser "Aéreo" obrigar informar uma das opções abaixo: * Atraso de produção * Venda aérea * A ser cobrado do cliente Caso o Modal não for aéreo, deixar a opção bloqueada. Precisará vincular o qvd CPC389 o nov</t>
+  </si>
+  <si>
+    <t>37216</t>
+  </si>
+  <si>
+    <t>Entrada de Conjuntos com qtd diferente</t>
+  </si>
+  <si>
+    <t>Boa tarde Flavio Conforme conversamos e foi ajustado pontualmente, temos a situação dois conjuntos com mesmo componente e quantidades diferentes. Abaixo os itens.</t>
+  </si>
+  <si>
+    <t>37276</t>
+  </si>
+  <si>
+    <t>Melhoria | QVD do Controle da Valorização - Reunião</t>
+  </si>
+  <si>
+    <t>Conforme conversado com o Felipe, fazer avaliação de como pode ser realizado o qvd do Controle da valorização, que tem base no F e do controle de coletas.</t>
+  </si>
+  <si>
+    <t>37382</t>
+  </si>
+  <si>
+    <t>Qualidade</t>
+  </si>
+  <si>
+    <t>Ajuste nas permissões dos usuários - Gestão de Ações</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos ajustar algumas permissões dos usuários no sistema Gestão de Ações. Componente: "CADASTROS", somente Admin´s podem ter acesso. Componente: "PLANO DE AÇÃO"(Cadastro), somente os Admin´s, Grupo de trabalho, Responsável pelo plano e responsável por ações, podem acessar seus planos n</t>
+  </si>
+  <si>
+    <t>Matheus Gonçalves</t>
+  </si>
+  <si>
+    <t>37374</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>Melhoria do sistema de Cadastros</t>
+  </si>
+  <si>
+    <t>Boa tarde, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1. Filtrar apelas as unidades de medida ativas no sistema. 1. Necessário aumentar a quantidade de caracteres no campo nomenclatura. ( no mínimo 100caracteres) 1. Colocar um botão d</t>
+  </si>
+  <si>
+    <t>Vanessa Knoth</t>
+  </si>
+  <si>
+    <t>35956</t>
+  </si>
+  <si>
+    <t>LISTAGEM DE NORMAS POR OTF</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor criar uma listagem de todas as OTFs produzidas de 01/01/2024 até 31/12/2025 correlacionando com a coluna "Norma Para Certificados" na tela WCPP221B de cada OTF. At.te</t>
+  </si>
+  <si>
+    <t>35977</t>
+  </si>
+  <si>
+    <t>Falha Sistema de Indicadores GIQ</t>
+  </si>
+  <si>
+    <t>Olá, No ano passado pedi para alterar o campo da média/acumulado para um campo editável, mas agora apareceu umas falhas no cálculo, então proponho as seguintes correções: 1) Na página de incluir as Metas do indicador, a média da meta deve ser um campo travado não editável e precisa ser calculada soz</t>
+  </si>
+  <si>
+    <t>Helena Mariana Segalla</t>
+  </si>
+  <si>
+    <t>36342</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Solicitação de ajuste de trava no sistema de inventário – WMS</t>
+  </si>
+  <si>
+    <t>Boa tarde! Precisamos realizar um ajuste no sistema de inventário do WMS. Atualmente, ao realizar inventário de materiais, o sistema emite uma mensagem de alerta quando existe uma pré‑lista em aberto, porém ainda permite a continuidade do processo. Já no caso de EPIs, o sistema não emite qualquer al</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>37114</t>
+  </si>
+  <si>
+    <t>sistema de cadastro de modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ao cadastrar um modelo com os mesmos que já tenha em outro cadastro, o mesmo desaparece do sistema, é necessário alterar esta formula, exemplo, hoje alterei o codigo do cliente deste modelo 1802380, o cadastro sumiu pois tem outro com o mesmo cadastro de cliente e material. Para um novo cadastro de </t>
+  </si>
+  <si>
+    <t>Fernando Beltrame</t>
+  </si>
+  <si>
+    <t>36502</t>
+  </si>
+  <si>
+    <t>qlik sense correção grafico 5s</t>
+  </si>
+  <si>
+    <t>qlik sense corrreção grafico 5s</t>
+  </si>
+  <si>
+    <t>Luiz Ricardo Bottin</t>
+  </si>
+  <si>
+    <t>37134</t>
+  </si>
+  <si>
+    <t>AJUSTES APONTAMENTO LINHA MESA REDONDA UPR</t>
+  </si>
+  <si>
+    <t>Bom dia, Iniciamos hoje (09/03/2026) os primeiros apontamentos na linha mesa redonda UPR, operador sugeriu para agilizar seu apontamento deixar as principais paradas de mais fácil acesso. Uma ideia muito inteligente que irá agilizar muito o processo de apontamento, ele não vai precisar ficar procura</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>37182</t>
+  </si>
+  <si>
+    <t>Análise</t>
+  </si>
+  <si>
+    <t>AJUSTES - EXTRAÇÃO DE DADOS APONTAMENTO LINHA MESAS REDONDAS</t>
+  </si>
+  <si>
+    <t>Bom dia, No dia 10/03/2026 iniciamos o piloto de apontamento eletrônico na linha mesas redondas, feito a extração em Excel notamos alguns pontos que precisam ser ajustados. * Coluna Y plan 1 (percentual executado) - puxando informações incorretas comparando com o que está sendo apontado no tablet. *</t>
+  </si>
+  <si>
+    <t>37174</t>
+  </si>
+  <si>
+    <t>UPR</t>
+  </si>
+  <si>
+    <t>Programação de ajustem APS</t>
+  </si>
+  <si>
+    <t>Boa tarde! Preparar arquivo QVD, para integração do ERP para o APS na programação da ajustagem: Local apontamento Modelo Tempo padrão Status Apontamento Nome operador Tipo operação Dúvidas a disposição! Obrigado! At.te,</t>
+  </si>
+  <si>
+    <t>Cristiano Nazário</t>
+  </si>
+  <si>
+    <t>37183</t>
+  </si>
+  <si>
+    <t>Retirada do (SIM)!</t>
+  </si>
+  <si>
+    <t>Bom dia, Por gentileza, preciso retirar a confirmação do (SIM), tanto na coleta quando na entrega. At.te</t>
+  </si>
+  <si>
+    <t>Johnny José Rocha</t>
+  </si>
+  <si>
+    <t>37170</t>
+  </si>
+  <si>
+    <t>Sistema de apontamento - pó de ferro</t>
+  </si>
+  <si>
+    <t>Boa tarde, preciso que seja feita algumas alterações no sistema de apontamento dos tablets. · Pesquisa de sequência no sistema do Tablet - com objetivo de verificar quando, por quem e como a peça foi cortada. · Aba movimentação de peças: não está sendo feita a movimentação de peça por mais que ela e</t>
+  </si>
+  <si>
+    <t>Amanda Vitoria Aroeira Marinho</t>
+  </si>
+  <si>
+    <t>37361</t>
+  </si>
+  <si>
+    <t>Base Histórica da Data de Reconhecimento  de Receita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
+  </si>
+  <si>
+    <t>37330</t>
+  </si>
+  <si>
+    <t>MELHORIAS NO APONTAEMNTO LINHA FASE 4 - UPR</t>
+  </si>
+  <si>
+    <t>Boa tarde, Estamos enfrentando uma dificuldade em dividir tempos na linha fase 4 que se encontra hoje em teste. Precisamos que o tempo da peça (sequência) que se encontra finalizada (100% indicado pelo operador) com retoques marcadas pela inspeção próximo a troca de turno, seja somado ao apontamento</t>
+  </si>
+  <si>
+    <t>37365</t>
+  </si>
+  <si>
+    <t>Pdf relacionad a dados testes de força.</t>
+  </si>
+  <si>
+    <t>Boa tarde! Solicito inserção de um pdf para visualizar os dados de teste de força na plataforma de ergonomia, igual aos pdf's que aparece na ficha de queixa. Desde já agradeço. At.te</t>
+  </si>
+  <si>
+    <t>Joice Kroening</t>
+  </si>
+  <si>
+    <t>37294</t>
+  </si>
+  <si>
+    <t>WMS - Abertura de chamado sem identificação</t>
+  </si>
+  <si>
+    <t>Bom dia Maciel, gentileza criar regra para abertura de chamado, para que seja obrigatório o preenchimento do código ou do contentor, pois esta gerando OM sem informação.</t>
+  </si>
+  <si>
+    <t>Rafael De Souza</t>
+  </si>
+  <si>
+    <t>37282</t>
+  </si>
+  <si>
+    <t>Inclusão do campo "Romaneio" na declaração de recebimento</t>
+  </si>
+  <si>
+    <t>Boa tarde! solicito a inclusão de busca por Romaneio na declaração de recebimento, pois nesses casos não conseguimos buscar para gerar a declaração.</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>37288</t>
+  </si>
+  <si>
+    <t>melhoria no sistema de inventário das embalagens</t>
+  </si>
+  <si>
+    <t>Bom dia! Com o aval do Rafael, solicito uma melhoria no sistema de inventário das embalagens (caixas Magayver). Atualmente, o sistema considera apenas as embalagens contadas fisicamente. Porém, existe a possibilidade de haver saldo no sistema mesmo quando a embalagem não existe fisicamente. Diante d</t>
+  </si>
+  <si>
+    <t>37354</t>
+  </si>
+  <si>
+    <t>saldo negativo EPI</t>
+  </si>
+  <si>
+    <t>Bom dia! Identificamos um problema de saldo negativo no ERP. Apesar disso, o sistema de pré-lista ainda está permitindo requisições e baixas, possivelmente porque há saldo disponível no estoque intermediário. Lembro que já havíamos solicitado a criação de uma trava na pré-lista para impedir requisiç</t>
+  </si>
+  <si>
+    <t>37255</t>
+  </si>
+  <si>
+    <t>Altona || Cadastro P&amp;D</t>
+  </si>
+  <si>
+    <t>Bom dia, Sandro! Solicito algumas melhorias na tela de cadastro do P&amp;D (imagem abaixo). 1) Liberar o acesso desse sistema para os funcionários abaixo: Paula Rosa Grando - 142830 Jeferson Borges - 131580 2) Incrementar automaticamente o número do projeto e sugerir um novo, mas não bloquear esse campo</t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>37368</t>
+  </si>
+  <si>
+    <t>Funções bloqueadas no sistema Gestão de Ações</t>
+  </si>
+  <si>
+    <t>Boa tarde, Segue uma nova ação de correção para o sistema Gestão de ações. Não consegui encontrar um padrão para este problema, mas as vezes o sistema deixa de funcionar. Nenhum botão ou aba responde, o problema só é solucionado ao recarregar a página. Video evidenciando o problema em anexo. Atencio</t>
+  </si>
+  <si>
+    <t>37370</t>
+  </si>
+  <si>
+    <t>Ações concluídas com problema - Gestão de ações.</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos corrigir uma função no sistema Gestão de Ações. As ações ficam concluídas somente quando há anexos que evidenciem a sua conclusão, se o anexo for removido a ação deve "abrir" novamente. Atualmente isso não acontece, em anexo segue um vídeo evidenciando. Z:\Winword\MATHEUS GONCA</t>
+  </si>
+  <si>
+    <t>37246</t>
+  </si>
+  <si>
+    <t>Usinagem</t>
+  </si>
+  <si>
+    <t>Falta de liberação após Colaborador retornar de férias.</t>
+  </si>
+  <si>
+    <t>Bom dia, Tudo bem? Estamos com uma dificuldade nos apontamentos MPO, Check-liste, PID, Movimentação, em relação aos operadores que retornam de férias ou afastamento. Atualmente, precisamos realizar um ticket para pedir liberação das permissões bloqueadas. Como a data de retorno ou período de ausênci</t>
+  </si>
+  <si>
+    <t>Tiago Bazzi Zancanella</t>
+  </si>
+  <si>
+    <t>11569480072</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>37001</t>
+  </si>
+  <si>
+    <t>Comparativo de horas paradas entre SMI e MES</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito um chamado para fazer um comparativo de horas paradas entre SMI e MESS, disponibilizando um dashboard na aplicação de controle de manutenção do QlikSense</t>
+  </si>
+  <si>
+    <t>35367</t>
+  </si>
+  <si>
+    <t>Indicadores MTTR e MDT - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
+  </si>
+  <si>
+    <t>36121</t>
+  </si>
+  <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
+    <t>Relatório de log e filtros de métodos de preventiva</t>
+  </si>
+  <si>
+    <t>Bom dia, Conversado pessoalmente. Att,</t>
+  </si>
+  <si>
+    <t>Enzo Luiz Okabe Auad</t>
+  </si>
+  <si>
+    <t>36320</t>
+  </si>
+  <si>
+    <t>Linkar gatilho de ACR com TV manutenções (Central + Usinagem)</t>
+  </si>
+  <si>
+    <t>Bom dia, Estou solicitando que façamos um link entre os gatilhos de ACR e a gestão visual nas TVs. A ideia é implementar gestão visual além da tarja amarela, sinalizando visualmente quando algum dos gatilhos forem atingidos (Tempo e frequencia) Att,</t>
+  </si>
+  <si>
+    <t>36232</t>
+  </si>
+  <si>
+    <t>Report técnico - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
+    <t>36213</t>
+  </si>
+  <si>
+    <t>Alteração no sistema de manutenção</t>
+  </si>
+  <si>
+    <t>Bom dia, Estamos solicitando que seja feito uma alteração no sistema de manutenção que envolve a seguinte mudança: Ordens preventivas e provenientes de métodos não devem ser programadas diretas, devem passar pela programação antes, ou seja, devem ser abertas com status de aguardando programação. Con</t>
+  </si>
+  <si>
+    <t>35527</t>
+  </si>
+  <si>
+    <t>Orçamento 2025</t>
+  </si>
+  <si>
+    <t>Boa tarde, Segue a planilha com a estrutura de orçamento, conforme alinhado na reunião. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Marcio Silva</t>
+  </si>
+  <si>
+    <t>37022</t>
+  </si>
+  <si>
+    <t>sistema de apontamento da lubrificação</t>
+  </si>
+  <si>
+    <t>Bom dia, precisamos inserir no sistema de manutenção um método de apontamento para os lubrificadores onde eles consigam colocar a quantidade de lubrificantes, tipo de lubrificantes e serviço. Para poder gerarmos relatórios de consumo e custos de lubrificante gasto . Podemos marcar uma reunião para a</t>
+  </si>
+  <si>
+    <t>Gerson Mendonça</t>
+  </si>
+  <si>
+    <t>36717</t>
+  </si>
+  <si>
+    <t>DATA LIMITE PARA BAIXA DE O.S</t>
+  </si>
+  <si>
+    <t>Bom dia, Gostaria de implementar uma opção no sistema de manutenção, onde possa ser limitado e/ou justificado o motivo da ordem não ter sido baixada no tempo hábil. Exemplo: Peguei uma O.S. no dia 17/02/2026, com a função habilitada e definida pelo usuário, tenho o limite de dias conforme a O.S. (em</t>
+  </si>
+  <si>
+    <t>Guilherme Ferreira</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Criar agendamento que dispare o envio do lote de produtos.</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>19909</t>
-  </si>
-  <si>
-    <t>Criar KB Genexus especifica para Registro de pinturas</t>
-  </si>
-  <si>
-    <t>36206</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - API</t>
-  </si>
-  <si>
-    <t>37015</t>
-  </si>
-  <si>
-    <t>DIFA Interno e fretes - Ajuste de observação fiscal - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Nas notas de DIFA interno e DIFA nos fretes precisa ser enviado os registros de observação fiscal e ajustes, conforme exemplo da NF 186758: O campo OBSERVACAO=@CODIGO(881) será o mesmo, o que vai mudar é o campo CODIGOAJUSTEBENEFICIO Nas notas de CFOP 1.556 e 1.551 o código de ajuste será S</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>33549</t>
-  </si>
-  <si>
-    <t>Integração de sistema Logística x data book - Relatório x Registro End's</t>
-  </si>
-  <si>
-    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
-  </si>
-  <si>
-    <t>Rosivaldo Silva</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>37160</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>Conversão da KB comercial para Gx18</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos migrar a aplicação do comercial, atualmente na versão gx75 para a versão 18. Principais entregas: - Levantar funcionalidades usadas e necessárias para a migração - Desenhar fluxo de trabalho com aplicação web - Converter objetos Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>30069</t>
-  </si>
-  <si>
-    <t>Controle de Importação - integração financeira</t>
-  </si>
-  <si>
-    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
-  </si>
-  <si>
-    <t>31836</t>
-  </si>
-  <si>
-    <t>Melhoria WMS - Conferencia e Carregamento</t>
-  </si>
-  <si>
-    <t>32150</t>
-  </si>
-  <si>
-    <t>Inventario WMS - Registro de Ajuste de Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
-  </si>
-  <si>
-    <t>34960</t>
-  </si>
-  <si>
-    <t>"Divergência no status da invoice - Precisa acessar a tela para atualizar o status"</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel, Gentileza vincular o campo do Status da Parcela do registro de cambio com o Status da Parcela da Invoice. Quando alterado para parcial ou pago no Registro de Cambio, deve ser atualizada a Invoice. Gentileza atualizar todo o histórico desde 2019 ajustando o sistema de Invoice. Exempl</t>
-  </si>
-  <si>
-    <t>36262</t>
-  </si>
-  <si>
-    <t>Melhoria | Vinculo de Atraso na Invoice</t>
-  </si>
-  <si>
-    <t>Boa tarde, Maciel, Criar uma opção na tela da Invoice abaixo, abaixo de modal que caso o Modal ser "Aéreo" obrigar informar uma das opções abaixo: * Atraso de produção * Venda aérea * A ser cobrado do cliente Caso o Modal não for aéreo, deixar a opção bloqueada. Precisará vincular o qvd CPC389 o nov</t>
-  </si>
-  <si>
-    <t>37216</t>
-  </si>
-  <si>
-    <t>Entrada de Conjuntos com qtd diferente</t>
-  </si>
-  <si>
-    <t>Boa tarde Flavio Conforme conversamos e foi ajustado pontualmente, temos a situação dois conjuntos com mesmo componente e quantidades diferentes. Abaixo os itens.</t>
-  </si>
-  <si>
-    <t>37276</t>
-  </si>
-  <si>
-    <t>Melhoria | QVD do Controle da Valorização - Reunião</t>
-  </si>
-  <si>
-    <t>Conforme conversado com o Felipe, fazer avaliação de como pode ser realizado o qvd do Controle da valorização, que tem base no F e do controle de coletas.</t>
-  </si>
-  <si>
-    <t>37382</t>
-  </si>
-  <si>
-    <t>Qualidade</t>
-  </si>
-  <si>
-    <t>Ajuste nas permissões dos usuários - Gestão de Ações</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos ajustar algumas permissões dos usuários no sistema Gestão de Ações. Componente: "CADASTROS", somente Admin´s podem ter acesso. Componente: "PLANO DE AÇÃO"(Cadastro), somente os Admin´s, Grupo de trabalho, Responsável pelo plano e responsável por ações, podem acessar seus planos n</t>
-  </si>
-  <si>
-    <t>Matheus Gonçalves</t>
-  </si>
-  <si>
-    <t>37374</t>
-  </si>
-  <si>
-    <t>Melhoria do sistema de Cadastros</t>
-  </si>
-  <si>
-    <t>Boa tarde, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1. Filtrar apelas as unidades de medida ativas no sistema. 1. Necessário aumentar a quantidade de caracteres no campo nomenclatura. ( no mínimo 100caracteres) 1. Colocar um botão d</t>
-  </si>
-  <si>
-    <t>Vanessa Knoth</t>
-  </si>
-  <si>
-    <t>35956</t>
-  </si>
-  <si>
-    <t>LISTAGEM DE NORMAS POR OTF</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor criar uma listagem de todas as OTFs produzidas de 01/01/2024 até 31/12/2025 correlacionando com a coluna "Norma Para Certificados" na tela WCPP221B de cada OTF. At.te</t>
-  </si>
-  <si>
-    <t>35977</t>
-  </si>
-  <si>
-    <t>Falha Sistema de Indicadores GIQ</t>
-  </si>
-  <si>
-    <t>Olá, No ano passado pedi para alterar o campo da média/acumulado para um campo editável, mas agora apareceu umas falhas no cálculo, então proponho as seguintes correções: 1) Na página de incluir as Metas do indicador, a média da meta deve ser um campo travado não editável e precisa ser calculada soz</t>
-  </si>
-  <si>
-    <t>Helena Mariana Segalla</t>
-  </si>
-  <si>
-    <t>36342</t>
-  </si>
-  <si>
-    <t>Almoxarifado</t>
-  </si>
-  <si>
-    <t>Solicitação de ajuste de trava no sistema de inventário – WMS</t>
-  </si>
-  <si>
-    <t>Boa tarde! Precisamos realizar um ajuste no sistema de inventário do WMS. Atualmente, ao realizar inventário de materiais, o sistema emite uma mensagem de alerta quando existe uma pré‑lista em aberto, porém ainda permite a continuidade do processo. Já no caso de EPIs, o sistema não emite qualquer al</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>37114</t>
-  </si>
-  <si>
-    <t>sistema de cadastro de modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ao cadastrar um modelo com os mesmos que já tenha em outro cadastro, o mesmo desaparece do sistema, é necessário alterar esta formula, exemplo, hoje alterei o codigo do cliente deste modelo 1802380, o cadastro sumiu pois tem outro com o mesmo cadastro de cliente e material. Para um novo cadastro de </t>
-  </si>
-  <si>
-    <t>Fernando Beltrame</t>
-  </si>
-  <si>
-    <t>36502</t>
-  </si>
-  <si>
-    <t>Fundição</t>
-  </si>
-  <si>
-    <t>qlik sense correção grafico 5s</t>
-  </si>
-  <si>
-    <t>qlik sense corrreção grafico 5s</t>
-  </si>
-  <si>
-    <t>Luiz Ricardo Bottin</t>
-  </si>
-  <si>
-    <t>37134</t>
-  </si>
-  <si>
-    <t>AJUSTES APONTAMENTO LINHA MESA REDONDA UPR</t>
-  </si>
-  <si>
-    <t>Bom dia, Iniciamos hoje (09/03/2026) os primeiros apontamentos na linha mesa redonda UPR, operador sugeriu para agilizar seu apontamento deixar as principais paradas de mais fácil acesso. Uma ideia muito inteligente que irá agilizar muito o processo de apontamento, ele não vai precisar ficar procura</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>37182</t>
-  </si>
-  <si>
-    <t>Análise</t>
-  </si>
-  <si>
-    <t>AJUSTES - EXTRAÇÃO DE DADOS APONTAMENTO LINHA MESAS REDONDAS</t>
-  </si>
-  <si>
-    <t>Bom dia, No dia 10/03/2026 iniciamos o piloto de apontamento eletrônico na linha mesas redondas, feito a extração em Excel notamos alguns pontos que precisam ser ajustados. * Coluna Y plan 1 (percentual executado) - puxando informações incorretas comparando com o que está sendo apontado no tablet. *</t>
-  </si>
-  <si>
-    <t>37174</t>
-  </si>
-  <si>
-    <t>Programação de ajustem APS</t>
-  </si>
-  <si>
-    <t>Boa tarde! Preparar arquivo QVD, para integração do ERP para o APS na programação da ajustagem: Local apontamento Modelo Tempo padrão Status Apontamento Nome operador Tipo operação Dúvidas a disposição! Obrigado! At.te,</t>
-  </si>
-  <si>
-    <t>Cristiano Nazário</t>
-  </si>
-  <si>
-    <t>37183</t>
-  </si>
-  <si>
-    <t>Logística</t>
-  </si>
-  <si>
-    <t>Retirada do (SIM)!</t>
-  </si>
-  <si>
-    <t>Bom dia, Por gentileza, preciso retirar a confirmação do (SIM), tanto na coleta quando na entrega. At.te</t>
-  </si>
-  <si>
-    <t>Johnny José Rocha</t>
-  </si>
-  <si>
-    <t>37170</t>
-  </si>
-  <si>
-    <t>Sistema de apontamento - pó de ferro</t>
-  </si>
-  <si>
-    <t>Boa tarde, preciso que seja feita algumas alterações no sistema de apontamento dos tablets. · Pesquisa de sequência no sistema do Tablet - com objetivo de verificar quando, por quem e como a peça foi cortada. · Aba movimentação de peças: não está sendo feita a movimentação de peça por mais que ela e</t>
-  </si>
-  <si>
-    <t>Amanda Vitoria Aroeira Marinho</t>
-  </si>
-  <si>
-    <t>37361</t>
-  </si>
-  <si>
-    <t>Base Histórica da Data de Reconhecimento  de Receita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
-  </si>
-  <si>
-    <t>37330</t>
-  </si>
-  <si>
-    <t>MELHORIAS NO APONTAEMNTO LINHA FASE 4 - UPR</t>
-  </si>
-  <si>
-    <t>Boa tarde, Estamos enfrentando uma dificuldade em dividir tempos na linha fase 4 que se encontra hoje em teste. Precisamos que o tempo da peça (sequência) que se encontra finalizada (100% indicado pelo operador) com retoques marcadas pela inspeção próximo a troca de turno, seja somado ao apontamento</t>
-  </si>
-  <si>
-    <t>37365</t>
-  </si>
-  <si>
-    <t>Pdf relacionad a dados testes de força.</t>
-  </si>
-  <si>
-    <t>Boa tarde! Solicito inserção de um pdf para visualizar os dados de teste de força na plataforma de ergonomia, igual aos pdf's que aparece na ficha de queixa. Desde já agradeço. At.te</t>
-  </si>
-  <si>
-    <t>Joice Kroening</t>
-  </si>
-  <si>
-    <t>37294</t>
-  </si>
-  <si>
-    <t>WMS - Abertura de chamado sem identificação</t>
-  </si>
-  <si>
-    <t>Bom dia Maciel, gentileza criar regra para abertura de chamado, para que seja obrigatório o preenchimento do código ou do contentor, pois esta gerando OM sem informação.</t>
-  </si>
-  <si>
-    <t>Rafael De Souza</t>
-  </si>
-  <si>
-    <t>37282</t>
-  </si>
-  <si>
-    <t>Inclusão do campo "Romaneio" na declaração de recebimento</t>
-  </si>
-  <si>
-    <t>Boa tarde! solicito a inclusão de busca por Romaneio na declaração de recebimento, pois nesses casos não conseguimos buscar para gerar a declaração.</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
+    <t>Laura Herrmann Schmickler</t>
+  </si>
+  <si>
+    <t>11569958658</t>
+  </si>
+  <si>
+    <t>Criar API para receber informações do MES para a abertura da SS</t>
+  </si>
+  <si>
+    <t>Ajustar as oportunidades já enviadas com a fase da oportunidade.</t>
+  </si>
+  <si>
+    <t>Processo para enviar exclusão de proposta / item</t>
+  </si>
+  <si>
+    <t>Teste unitário com usuário - cliente.</t>
+  </si>
+  <si>
+    <t>Teste unitário com usuário - produto.</t>
+  </si>
+  <si>
+    <t>Processo para enviar exclusão de oportunidades / proposta / item (copy)</t>
+  </si>
+  <si>
+    <t>Processo para enviar exclusão de item.</t>
+  </si>
+  <si>
+    <t>Teste unitário com usuário - oportunidade.</t>
+  </si>
+  <si>
+    <t>27802</t>
+  </si>
+  <si>
+    <t>Correções no chamado 26721 - Controle na geração de Sequencias (copy)</t>
+  </si>
+  <si>
+    <t>Boa tarde Flavio, Conforme falamos pelo Teams o relatório criado para controle na geração de sequencias, que estamos avaliando continua apresentando desvios. Precisamos entender o que vem ocasionando estes desvios, o plano de ação junto da GIQ continua em aberto até conseguirmos implantar este chama</t>
+  </si>
+  <si>
+    <t>Gilsimar Carls</t>
+  </si>
+  <si>
+    <t>11569522657</t>
+  </si>
+  <si>
+    <t>Multiplos de Caixa de ferro</t>
+  </si>
+  <si>
+    <t>37133</t>
+  </si>
+  <si>
+    <t>Quebra de lote para criação de pendência</t>
+  </si>
+  <si>
+    <t>boa tarde, Conforme conversado na reunião de hoje (09/03), favor liberar quebra de lote para setor da usinagem. Hoje, não há possibilidade de criar pendência sem ter que movimentar todo o lote. É importante que tenha essa possibilidade para melhorar nosso rastreio e aberturas de retrabalhos corretam</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Poburko</t>
+  </si>
+  <si>
+    <t>11569497169</t>
+  </si>
+  <si>
+    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>11569498823</t>
+  </si>
+  <si>
+    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada (copy)</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy)</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
+  </si>
+  <si>
+    <t>36482</t>
+  </si>
+  <si>
+    <t>Estorno para inventário</t>
+  </si>
+  <si>
+    <t>Identificamos a necessidade de criar uma nova funcionalidade no sistema de inventário, válida para todas as modalidades: a opção de estornar inventário. Atualmente, quando ocorre algum erro, precisamos estornar item por item, o que demanda um tempo significativo e impacta diretamente na agilidade da</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>33631</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - Custos - Reunião</t>
+  </si>
+  <si>
+    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
+  </si>
+  <si>
+    <t>Marcelo Americo</t>
+  </si>
+  <si>
+    <t>34225</t>
+  </si>
+  <si>
+    <t>Correções Relatório Faturamento por Sequência - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Sandro, bom dia! Solicito melhorias a seguir no Relatório Faturamento por Sequência. * Desconsiderar NF que não se tratam de venda (receita), por exemplo 210982/212675/213384/213385 (CFOP 5.949./6.949/7.949 - Remessa Conserto e Outros) NFe 213069 valor incorreto retornado no relatório.</t>
+  </si>
+  <si>
+    <t>36541</t>
+  </si>
+  <si>
+    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
+  </si>
+  <si>
+    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
+  </si>
+  <si>
+    <t>Alini Ferreira Ganda</t>
+  </si>
+  <si>
+    <t>35738</t>
+  </si>
+  <si>
+    <t>Melhoria apontamento de corte de canais - APONTAMENTO EM LOTE</t>
+  </si>
+  <si>
+    <t>Bom dia, Melhoria no apontamento de peças do sistema de corte de canais eletrônico, talvez criar um campo de pergunta se o cortador vai cortar 1 peça ou uma penca, se for penca abrir uma lista onde ele possa inserir todas as sequência de uma vez sem ter que ficar digitando todas as informações em ca</t>
+  </si>
+  <si>
+    <t>11569526882</t>
+  </si>
+  <si>
+    <t>ALTC - Verificar Retrabalho</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>37394</t>
+  </si>
+  <si>
+    <t>Rateio Jato Dirigido 1 e 2 - Adicionar operacoes na aplicação WEB</t>
+  </si>
+  <si>
+    <t>Boa tarde, Hoje (20/03/26 ) foi criado as operações jato dirigido para cadastrarmos os tempos na CPP para rateio de tempo Qlik. Precisamos que esse rateio seja retroativo. No apontamento eletrônico o estado da peça era somente apontado para informação e não apontado sua real operação. Precisamos que</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>36335</t>
+  </si>
+  <si>
+    <t>Ajuste em gráficos no B.I</t>
+  </si>
+  <si>
+    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
+  </si>
+  <si>
+    <t>Matheus Rodrigues de Almeida</t>
+  </si>
+  <si>
+    <t>Rateio Jato Dirigido 1 e 2 - Fazer QG para atualizar operações na apon3 com base no estado da peça</t>
+  </si>
+  <si>
+    <t>34335</t>
+  </si>
+  <si>
+    <t>Excelência Operacional</t>
+  </si>
+  <si>
+    <t>Tempo Padrão - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia Srs., Favor criar uma aplicação que traga os tempos padrões cadastrados que estão sendo usados para cálculo do IROG. Trazer de todos os setores (Acabamento, Usinagem, Inspeção, Moldagem,...) Disponibilizar o ícone na aplicação IROG: Trazer as seguintes informações: * Modelo; * Operação; * Te</t>
+  </si>
+  <si>
+    <t>Gabriel Lucas Kertichka</t>
+  </si>
+  <si>
+    <t>37200</t>
+  </si>
+  <si>
+    <t>Bloco 1: Estrutura Base e Telas Auxiliares</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos da elaboração de um sistema web para o corte escarfa UPR. São duas linhas apontadas por um operador simultaneamente (linha 1 e linha 2), Pra facilitar visual do operador e dinâmica dividir as duas linhas na mesma tela, mas com todos os resultados separados. As sequencias devem se</t>
+  </si>
+  <si>
+    <t>Bloco 2: Tela Principal - Lógica de Lote e Estado</t>
+  </si>
+  <si>
+    <t>Bloco 3: Tela Principal - Fechamento e Integração</t>
+  </si>
+  <si>
+    <t>Bloco 4: Revisão de Layout e Testes</t>
+  </si>
+  <si>
+    <t>11584865150</t>
+  </si>
+  <si>
+    <t>Tela de Cadastro de Turmas</t>
+  </si>
+  <si>
+    <t>37129</t>
+  </si>
+  <si>
+    <t>Esses relatórios também devem estar disponíveis na aba de relatórios para extração em excel a qualquer momento</t>
+  </si>
+  <si>
+    <t>Bom dia, Chamado Prioritário para correção de não conformidade identificada durante auditoria terceirizada não oficial da ISO 9001. Recentemente foi feita uma alteração no sistema na qual as ordens preventivas ao checar na caixa ilustrada abaixo sejam abertas como uma SS (solicitação de serviço) com</t>
+  </si>
+  <si>
+    <t>37403</t>
+  </si>
+  <si>
+    <t>Ofertas de conjuntos</t>
+  </si>
+  <si>
+    <t>@Maciel, Poderia remover o campo "Qty.:" dos componentes quando for oferta de conjunto? Tanto de Brasil quanto de exportação, pois essa quantidade é o número de placas no modelo, não tem necessidade de aparecer na oferta para o cliente. Obrigada!!</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>36677</t>
+  </si>
+  <si>
+    <t>Tempo realizado sem rateio</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor verificar a questão de rateio da etapa entre apontamentos de máquina, encontrei a seq. 853MD sem tempo padrão rateio, segue exemplo abaixo: Att,</t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>Data Limite Os/Report Técnico - Análise com equipe da manutenção - Reunião</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Dashboard de Change Log - Governança de TI</t>
+  </si>
+  <si>
+    <t>Período</t>
+  </si>
+  <si>
+    <t>Fev/2026</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Tickets corporativos para intranet / Power BI / Excel</t>
+  </si>
+  <si>
+    <t>Total de tickets</t>
+  </si>
+  <si>
+    <t>% dentro do SLA</t>
+  </si>
+  <si>
+    <t>Tempo médio (dias)</t>
+  </si>
+  <si>
+    <t>Áreas atendidas</t>
+  </si>
+  <si>
+    <t>Status final</t>
+  </si>
+  <si>
+    <t>Encerrado</t>
+  </si>
+  <si>
+    <t>Resumo Executivo</t>
+  </si>
+  <si>
+    <t>Tickets por Área</t>
+  </si>
+  <si>
+    <t>Distribuição por Tipo</t>
+  </si>
+  <si>
+    <t>Cumprimento SLA (15 dias)</t>
+  </si>
+  <si>
+    <t>Status Final</t>
+  </si>
+  <si>
+    <t>Tickets por Semana</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Muito Alta</t>
   </si>
   <si>
     <t>Sim</t>
   </si>
   <si>
-    <t>37288</t>
-  </si>
-  <si>
-    <t>melhoria no sistema de inventário das embalagens</t>
-  </si>
-  <si>
-    <t>Bom dia! Com o aval do Rafael, solicito uma melhoria no sistema de inventário das embalagens (caixas Magayver). Atualmente, o sistema considera apenas as embalagens contadas fisicamente. Porém, existe a possibilidade de haver saldo no sistema mesmo quando a embalagem não existe fisicamente. Diante d</t>
-  </si>
-  <si>
-    <t>37354</t>
-  </si>
-  <si>
-    <t>saldo negativo EPI</t>
-  </si>
-  <si>
-    <t>Bom dia! Identificamos um problema de saldo negativo no ERP. Apesar disso, o sistema de pré-lista ainda está permitindo requisições e baixas, possivelmente porque há saldo disponível no estoque intermediário. Lembro que já havíamos solicitado a criação de uma trava na pré-lista para impedir requisiç</t>
-  </si>
-  <si>
-    <t>37255</t>
-  </si>
-  <si>
-    <t>Altona || Cadastro P&amp;D</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Solicito algumas melhorias na tela de cadastro do P&amp;D (imagem abaixo). 1) Liberar o acesso desse sistema para os funcionários abaixo: Paula Rosa Grando - 142830 Jeferson Borges - 131580 2) Incrementar automaticamente o número do projeto e sugerir um novo, mas não bloquear esse campo</t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>37368</t>
-  </si>
-  <si>
-    <t>Funções bloqueadas no sistema Gestão de Ações</t>
-  </si>
-  <si>
-    <t>Boa tarde, Segue uma nova ação de correção para o sistema Gestão de ações. Não consegui encontrar um padrão para este problema, mas as vezes o sistema deixa de funcionar. Nenhum botão ou aba responde, o problema só é solucionado ao recarregar a página. Video evidenciando o problema em anexo. Atencio</t>
-  </si>
-  <si>
-    <t>37370</t>
-  </si>
-  <si>
-    <t>Ações concluídas com problema - Gestão de ações.</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos corrigir uma função no sistema Gestão de Ações. As ações ficam concluídas somente quando há anexos que evidenciem a sua conclusão, se o anexo for removido a ação deve "abrir" novamente. Atualmente isso não acontece, em anexo segue um vídeo evidenciando. Z:\Winword\MATHEUS GONCA</t>
-  </si>
-  <si>
-    <t>37246</t>
-  </si>
-  <si>
-    <t>Falta de liberação após Colaborador retornar de férias.</t>
-  </si>
-  <si>
-    <t>Bom dia, Tudo bem? Estamos com uma dificuldade nos apontamentos MPO, Check-liste, PID, Movimentação, em relação aos operadores que retornam de férias ou afastamento. Atualmente, precisamos realizar um ticket para pedir liberação das permissões bloqueadas. Como a data de retorno ou período de ausênci</t>
-  </si>
-  <si>
-    <t>Tiago Bazzi Zancanella</t>
-  </si>
-  <si>
-    <t>23838</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
-  </si>
-  <si>
-    <t>37001</t>
-  </si>
-  <si>
-    <t>Comparativo de horas paradas entre SMI e MES</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito um chamado para fazer um comparativo de horas paradas entre SMI e MESS, disponibilizando um dashboard na aplicação de controle de manutenção do QlikSense</t>
-  </si>
-  <si>
-    <t>35367</t>
-  </si>
-  <si>
-    <t>Indicadores MTTR e MDT - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
-  </si>
-  <si>
-    <t>36121</t>
-  </si>
-  <si>
-    <t>Relatório de log e filtros de métodos de preventiva</t>
-  </si>
-  <si>
-    <t>Bom dia, Conversado pessoalmente. Att,</t>
-  </si>
-  <si>
-    <t>Enzo Luiz Okabe Auad</t>
-  </si>
-  <si>
-    <t>36320</t>
-  </si>
-  <si>
-    <t>Linkar gatilho de ACR com TV manutenções (Central + Usinagem)</t>
-  </si>
-  <si>
-    <t>Bom dia, Estou solicitando que façamos um link entre os gatilhos de ACR e a gestão visual nas TVs. A ideia é implementar gestão visual além da tarja amarela, sinalizando visualmente quando algum dos gatilhos forem atingidos (Tempo e frequencia) Att,</t>
-  </si>
-  <si>
-    <t>36232</t>
-  </si>
-  <si>
-    <t>Report técnico - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
-  </si>
-  <si>
-    <t>36213</t>
-  </si>
-  <si>
-    <t>Alteração no sistema de manutenção</t>
-  </si>
-  <si>
-    <t>Bom dia, Estamos solicitando que seja feito uma alteração no sistema de manutenção que envolve a seguinte mudança: Ordens preventivas e provenientes de métodos não devem ser programadas diretas, devem passar pela programação antes, ou seja, devem ser abertas com status de aguardando programação. Con</t>
-  </si>
-  <si>
-    <t>35527</t>
-  </si>
-  <si>
-    <t>Orçamento 2025</t>
-  </si>
-  <si>
-    <t>Boa tarde, Segue a planilha com a estrutura de orçamento, conforme alinhado na reunião. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Marcio Silva</t>
-  </si>
-  <si>
-    <t>37022</t>
-  </si>
-  <si>
-    <t>sistema de apontamento da lubrificação</t>
-  </si>
-  <si>
-    <t>Bom dia, precisamos inserir no sistema de manutenção um método de apontamento para os lubrificadores onde eles consigam colocar a quantidade de lubrificantes, tipo de lubrificantes e serviço. Para poder gerarmos relatórios de consumo e custos de lubrificante gasto . Podemos marcar uma reunião para a</t>
-  </si>
-  <si>
-    <t>Gerson Mendonça</t>
-  </si>
-  <si>
-    <t>36717</t>
-  </si>
-  <si>
-    <t>DATA LIMITE PARA BAIXA DE O.S</t>
-  </si>
-  <si>
-    <t>Bom dia, Gostaria de implementar uma opção no sistema de manutenção, onde possa ser limitado e/ou justificado o motivo da ordem não ter sido baixada no tempo hábil. Exemplo: Peguei uma O.S. no dia 17/02/2026, com a função habilitada e definida pelo usuário, tenho o limite de dias conforme a O.S. (em</t>
-  </si>
-  <si>
-    <t>Guilherme Ferreira</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Criar agendamento que dispare o envio do lote de produtos.</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
-    <t>35890</t>
-  </si>
-  <si>
-    <t>Criar API para receber informações do MES para a abertura da SS</t>
-  </si>
-  <si>
-    <t>Ajustar as oportunidades já enviadas com a fase da oportunidade.</t>
-  </si>
-  <si>
-    <t>Processo para enviar exclusão de proposta / item</t>
-  </si>
-  <si>
-    <t>Teste unitário com usuário - cliente.</t>
-  </si>
-  <si>
-    <t>Teste unitário com usuário - produto.</t>
-  </si>
-  <si>
-    <t>Processo para enviar exclusão de oportunidades / proposta / item (copy)</t>
-  </si>
-  <si>
-    <t>Processo para enviar exclusão de item.</t>
-  </si>
-  <si>
-    <t>Teste unitário com usuário - oportunidade.</t>
-  </si>
-  <si>
-    <t>27802</t>
-  </si>
-  <si>
-    <t>Correções no chamado 26721 - Controle na geração de Sequencias (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde Flavio, Conforme falamos pelo Teams o relatório criado para controle na geração de sequencias, que estamos avaliando continua apresentando desvios. Precisamos entender o que vem ocasionando estes desvios, o plano de ação junto da GIQ continua em aberto até conseguirmos implantar este chama</t>
-  </si>
-  <si>
-    <t>Gilsimar Carls</t>
-  </si>
-  <si>
-    <t>36632</t>
-  </si>
-  <si>
-    <t>Multiplos de Caixa de ferro</t>
-  </si>
-  <si>
-    <t>37133</t>
-  </si>
-  <si>
-    <t>Quebra de lote para criação de pendência</t>
-  </si>
-  <si>
-    <t>boa tarde, Conforme conversado na reunião de hoje (09/03), favor liberar quebra de lote para setor da usinagem. Hoje, não há possibilidade de criar pendência sem ter que movimentar todo o lote. É importante que tenha essa possibilidade para melhorar nosso rastreio e aberturas de retrabalhos corretam</t>
-  </si>
-  <si>
-    <t>Pedro Henrique Poburko</t>
-  </si>
-  <si>
-    <t>32079</t>
-  </si>
-  <si>
-    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada (copy)</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy)</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
-  </si>
-  <si>
-    <t>36482</t>
-  </si>
-  <si>
-    <t>Estorno para inventário</t>
-  </si>
-  <si>
-    <t>Identificamos a necessidade de criar uma nova funcionalidade no sistema de inventário, válida para todas as modalidades: a opção de estornar inventário. Atualmente, quando ocorre algum erro, precisamos estornar item por item, o que demanda um tempo significativo e impacta diretamente na agilidade da</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>33631</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - Custos - Reunião</t>
-  </si>
-  <si>
-    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
-  </si>
-  <si>
-    <t>Marcelo Americo</t>
-  </si>
-  <si>
-    <t>34225</t>
-  </si>
-  <si>
-    <t>Correções Relatório Faturamento por Sequência - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Sandro, bom dia! Solicito melhorias a seguir no Relatório Faturamento por Sequência. * Desconsiderar NF que não se tratam de venda (receita), por exemplo 210982/212675/213384/213385 (CFOP 5.949./6.949/7.949 - Remessa Conserto e Outros) NFe 213069 valor incorreto retornado no relatório.</t>
-  </si>
-  <si>
-    <t>36541</t>
-  </si>
-  <si>
-    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
-  </si>
-  <si>
-    <t>35738</t>
-  </si>
-  <si>
-    <t>Melhoria apontamento de corte de canais - APONTAMENTO EM LOTE</t>
-  </si>
-  <si>
-    <t>Bom dia, Melhoria no apontamento de peças do sistema de corte de canais eletrônico, talvez criar um campo de pergunta se o cortador vai cortar 1 peça ou uma penca, se for penca abrir uma lista onde ele possa inserir todas as sequência de uma vez sem ter que ficar digitando todas as informações em ca</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>ALTC - Verificar Retrabalho</t>
-  </si>
-  <si>
-    <t>37394</t>
-  </si>
-  <si>
-    <t>Rateio Jato Dirigido 1 e 2 - Adicionar operacoes na aplicação WEB</t>
-  </si>
-  <si>
-    <t>Boa tarde, Hoje (20/03/26 ) foi criado as operações jato dirigido para cadastrarmos os tempos na CPP para rateio de tempo Qlik. Precisamos que esse rateio seja retroativo. No apontamento eletrônico o estado da peça era somente apontado para informação e não apontado sua real operação. Precisamos que</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>20/05/2026</t>
-  </si>
-  <si>
-    <t>36335</t>
-  </si>
-  <si>
-    <t>Ajuste em gráficos no B.I</t>
-  </si>
-  <si>
-    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
-  </si>
-  <si>
-    <t>Matheus Rodrigues de Almeida</t>
-  </si>
-  <si>
-    <t>Rateio Jato Dirigido 1 e 2 - Fazer QG para atualizar operações na apon3 com base no estado da peça</t>
-  </si>
-  <si>
-    <t>34335</t>
-  </si>
-  <si>
-    <t>Excelência Operacional</t>
-  </si>
-  <si>
-    <t>Tempo Padrão - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia Srs., Favor criar uma aplicação que traga os tempos padrões cadastrados que estão sendo usados para cálculo do IROG. Trazer de todos os setores (Acabamento, Usinagem, Inspeção, Moldagem,...) Disponibilizar o ícone na aplicação IROG: Trazer as seguintes informações: * Modelo; * Operação; * Te</t>
-  </si>
-  <si>
-    <t>Gabriel Lucas Kertichka</t>
-  </si>
-  <si>
-    <t>37200</t>
-  </si>
-  <si>
-    <t>Bloco 1: Estrutura Base e Telas Auxiliares</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos da elaboração de um sistema web para o corte escarfa UPR. São duas linhas apontadas por um operador simultaneamente (linha 1 e linha 2), Pra facilitar visual do operador e dinâmica dividir as duas linhas na mesma tela, mas com todos os resultados separados. As sequencias devem se</t>
-  </si>
-  <si>
-    <t>Bloco 2: Tela Principal - Lógica de Lote e Estado</t>
-  </si>
-  <si>
-    <t>Bloco 3: Tela Principal - Fechamento e Integração</t>
-  </si>
-  <si>
-    <t>Bloco 4: Revisão de Layout e Testes</t>
-  </si>
-  <si>
-    <t>35764</t>
-  </si>
-  <si>
-    <t>Tela de Cadastro de Turmas</t>
-  </si>
-  <si>
-    <t>37129</t>
-  </si>
-  <si>
-    <t>Esses relatórios também devem estar disponíveis na aba de relatórios para extração em excel a qualquer momento</t>
-  </si>
-  <si>
-    <t>Bom dia, Chamado Prioritário para correção de não conformidade identificada durante auditoria terceirizada não oficial da ISO 9001. Recentemente foi feita uma alteração no sistema na qual as ordens preventivas ao checar na caixa ilustrada abaixo sejam abertas como uma SS (solicitação de serviço) com</t>
-  </si>
-  <si>
-    <t>37403</t>
-  </si>
-  <si>
-    <t>Ofertas de conjuntos</t>
-  </si>
-  <si>
-    <t>@Maciel, Poderia remover o campo "Qty.:" dos componentes quando for oferta de conjunto? Tanto de Brasil quanto de exportação, pois essa quantidade é o número de placas no modelo, não tem necessidade de aparecer na oferta para o cliente. Obrigada!!</t>
-  </si>
-  <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>36677</t>
-  </si>
-  <si>
-    <t>Usinagem</t>
-  </si>
-  <si>
-    <t>Tempo realizado sem rateio</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor verificar a questão de rateio da etapa entre apontamentos de máquina, encontrei a seq. 853MD sem tempo padrão rateio, segue exemplo abaixo: Att,</t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>26/03/2026</t>
-  </si>
-  <si>
-    <t>Data Limite Os/Report Técnico - Análise com equipe da manutenção - Reunião</t>
-  </si>
-  <si>
-    <t>01/04/2026</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>Dashboard de Change Log - Governança de TI</t>
-  </si>
-  <si>
-    <t>Período</t>
-  </si>
-  <si>
-    <t>SPRINT 2026-10</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Tickets corporativos para intranet / Power BI / Excel</t>
-  </si>
-  <si>
-    <t>Total de tickets</t>
-  </si>
-  <si>
-    <t>% dentro do SLA</t>
-  </si>
-  <si>
-    <t>Tempo médio (dias)</t>
-  </si>
-  <si>
-    <t>Áreas atendidas</t>
-  </si>
-  <si>
-    <t>Status final</t>
-  </si>
-  <si>
-    <t>Encerrado</t>
-  </si>
-  <si>
-    <t>Resumo Executivo</t>
-  </si>
-  <si>
-    <t>Tickets por Área</t>
-  </si>
-  <si>
-    <t>Distribuição por Tipo</t>
-  </si>
-  <si>
-    <t>Cumprimento SLA (15 dias)</t>
-  </si>
-  <si>
-    <t>Status Final</t>
-  </si>
-  <si>
-    <t>Tickets por Semana</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Muito Alta</t>
-  </si>
-  <si>
     <t>Abertos</t>
   </si>
   <si>
@@ -1165,6 +1198,9 @@
   </si>
   <si>
     <t>Não definida</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Fila</t>
@@ -1804,7 +1840,7 @@
         <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
@@ -1813,16 +1849,16 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>23</v>
@@ -1848,43 +1884,43 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>59</v>
@@ -1898,7 +1934,7 @@
         <v>60</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -1907,22 +1943,22 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>25</v>
@@ -1942,10 +1978,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
@@ -1954,22 +1990,22 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>25</v>
@@ -1981,7 +2017,7 @@
         <v>27</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>40</v>
@@ -1989,10 +2025,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
@@ -2001,16 +2037,16 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>23</v>
@@ -2036,10 +2072,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
@@ -2048,22 +2084,22 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>25</v>
@@ -2075,7 +2111,7 @@
         <v>27</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>40</v>
@@ -2083,10 +2119,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -2095,22 +2131,22 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>25</v>
@@ -2130,34 +2166,34 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -2177,28 +2213,28 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>23</v>
@@ -2224,7 +2260,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
@@ -2233,34 +2269,34 @@
         <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>59</v>
@@ -2271,7 +2307,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>42</v>
@@ -2280,34 +2316,34 @@
         <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>59</v>
@@ -2318,43 +2354,43 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>59</v>
@@ -2365,37 +2401,37 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>26</v>
@@ -2412,10 +2448,10 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
@@ -2424,16 +2460,16 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>23</v>
@@ -2459,10 +2495,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>17</v>
@@ -2471,34 +2507,34 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>29</v>
@@ -2506,10 +2542,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>17</v>
@@ -2518,31 +2554,31 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>59</v>
@@ -2553,46 +2589,46 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>29</v>
@@ -2600,46 +2636,46 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>29</v>
@@ -2647,37 +2683,37 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>38</v>
@@ -2686,7 +2722,7 @@
         <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>29</v>
@@ -2694,34 +2730,34 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>37</v>
@@ -2733,7 +2769,7 @@
         <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>29</v>
@@ -2741,34 +2777,34 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>25</v>
@@ -2780,7 +2816,7 @@
         <v>27</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>29</v>
@@ -2788,34 +2824,34 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>25</v>
@@ -2827,7 +2863,7 @@
         <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>29</v>
@@ -2835,10 +2871,10 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>17</v>
@@ -2847,22 +2883,22 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>25</v>
@@ -2874,7 +2910,7 @@
         <v>27</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>29</v>
@@ -2882,10 +2918,10 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
@@ -2894,22 +2930,22 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>25</v>
@@ -2921,7 +2957,7 @@
         <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>29</v>
@@ -2929,10 +2965,10 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>17</v>
@@ -2941,22 +2977,22 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>25</v>
@@ -2968,7 +3004,7 @@
         <v>27</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>29</v>
@@ -2976,10 +3012,10 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
@@ -2988,22 +3024,22 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>25</v>
@@ -3015,7 +3051,7 @@
         <v>27</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>29</v>
@@ -3023,7 +3059,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>31</v>
@@ -3035,10 +3071,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>21</v>
@@ -3050,7 +3086,7 @@
         <v>23</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>25</v>
@@ -3062,7 +3098,7 @@
         <v>27</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>29</v>
@@ -3070,10 +3106,10 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>17</v>
@@ -3082,22 +3118,22 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>25</v>
@@ -3109,7 +3145,7 @@
         <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>29</v>
@@ -3117,10 +3153,10 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>17</v>
@@ -3129,22 +3165,22 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>25</v>
@@ -3156,7 +3192,7 @@
         <v>27</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>29</v>
@@ -3164,10 +3200,10 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>17</v>
@@ -3176,22 +3212,22 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>25</v>
@@ -3203,7 +3239,7 @@
         <v>27</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>29</v>
@@ -3211,10 +3247,10 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>17</v>
@@ -3223,22 +3259,22 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>25</v>
@@ -3250,7 +3286,7 @@
         <v>27</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>29</v>
@@ -3258,10 +3294,10 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>17</v>
@@ -3270,22 +3306,22 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>25</v>
@@ -3297,7 +3333,7 @@
         <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>29</v>
@@ -3305,34 +3341,34 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>46</v>
@@ -3344,7 +3380,7 @@
         <v>27</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>29</v>
@@ -3352,10 +3388,10 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>42</v>
+        <v>193</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>17</v>
@@ -3364,22 +3400,22 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>25</v>
@@ -3391,7 +3427,7 @@
         <v>27</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>29</v>
@@ -3399,10 +3435,10 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
@@ -3411,22 +3447,22 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>25</v>
@@ -3438,7 +3474,7 @@
         <v>27</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>29</v>
@@ -3446,10 +3482,10 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>17</v>
@@ -3458,22 +3494,22 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>25</v>
@@ -3485,7 +3521,7 @@
         <v>27</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>29</v>
@@ -3493,10 +3529,10 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>17</v>
@@ -3505,34 +3541,34 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>29</v>
@@ -3540,10 +3576,10 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>17</v>
@@ -3552,22 +3588,22 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>37</v>
@@ -3579,7 +3615,7 @@
         <v>27</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>29</v>
@@ -3587,7 +3623,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>42</v>
@@ -3599,22 +3635,22 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>25</v>
@@ -3626,7 +3662,7 @@
         <v>27</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>29</v>
@@ -3634,10 +3670,10 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>17</v>
@@ -3646,22 +3682,22 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>25</v>
@@ -3673,7 +3709,7 @@
         <v>27</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>29</v>
@@ -3681,10 +3717,10 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>17</v>
@@ -3693,34 +3729,34 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>214</v>
+        <v>27</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>29</v>
@@ -3728,10 +3764,10 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>17</v>
@@ -3740,34 +3776,34 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>46</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>29</v>
@@ -3775,34 +3811,34 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>25</v>
@@ -3814,7 +3850,7 @@
         <v>27</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>29</v>
@@ -3822,10 +3858,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
@@ -3834,25 +3870,25 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>26</v>
@@ -3861,7 +3897,7 @@
         <v>27</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>29</v>
@@ -3869,10 +3905,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
@@ -3881,22 +3917,22 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>25</v>
@@ -3908,7 +3944,7 @@
         <v>27</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>29</v>
@@ -3916,10 +3952,10 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>17</v>
@@ -3928,22 +3964,22 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>25</v>
@@ -3955,7 +3991,7 @@
         <v>27</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>29</v>
@@ -3963,10 +3999,10 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>42</v>
+        <v>241</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
@@ -3975,22 +4011,22 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>25</v>
@@ -4002,7 +4038,7 @@
         <v>27</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>29</v>
@@ -4010,37 +4046,37 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>95</v>
+        <v>249</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>26</v>
@@ -4057,10 +4093,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
@@ -4069,31 +4105,31 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>46</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>39</v>
@@ -4104,10 +4140,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
@@ -4116,22 +4152,22 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>37</v>
@@ -4151,10 +4187,10 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>17</v>
@@ -4163,22 +4199,22 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>25</v>
@@ -4198,10 +4234,10 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>17</v>
@@ -4210,22 +4246,22 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>25</v>
@@ -4245,10 +4281,10 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>17</v>
@@ -4257,22 +4293,22 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>37</v>
@@ -4292,10 +4328,10 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>17</v>
@@ -4304,22 +4340,22 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>25</v>
@@ -4339,10 +4375,10 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>17</v>
@@ -4351,31 +4387,31 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>39</v>
@@ -4386,10 +4422,10 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>17</v>
@@ -4398,22 +4434,22 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>25</v>
@@ -4433,10 +4469,10 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>17</v>
@@ -4445,22 +4481,22 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>25</v>
@@ -4480,10 +4516,10 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>272</v>
+        <v>103</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>17</v>
@@ -4492,25 +4528,25 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>95</v>
+        <v>284</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>95</v>
+        <v>248</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>26</v>
@@ -4527,7 +4563,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>42</v>
@@ -4536,28 +4572,28 @@
         <v>17</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>26</v>
@@ -4574,10 +4610,10 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>272</v>
+        <v>103</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>17</v>
@@ -4586,25 +4622,25 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>95</v>
+        <v>284</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>95</v>
+        <v>248</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>26</v>
@@ -4621,10 +4657,10 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>272</v>
+        <v>103</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>17</v>
@@ -4633,25 +4669,25 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>95</v>
+        <v>284</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>95</v>
+        <v>248</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>26</v>
@@ -4668,10 +4704,10 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>272</v>
+        <v>103</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>17</v>
@@ -4680,25 +4716,25 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>95</v>
+        <v>284</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>95</v>
+        <v>248</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>26</v>
@@ -4715,10 +4751,10 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>272</v>
+        <v>103</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>17</v>
@@ -4727,25 +4763,25 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>95</v>
+        <v>284</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>95</v>
+        <v>248</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>26</v>
@@ -4762,10 +4798,10 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>272</v>
+        <v>103</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>17</v>
@@ -4774,25 +4810,25 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>95</v>
+        <v>284</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>26</v>
@@ -4809,10 +4845,10 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>272</v>
+        <v>103</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>17</v>
@@ -4821,25 +4857,25 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>95</v>
+        <v>284</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>26</v>
@@ -4856,10 +4892,10 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>272</v>
+        <v>103</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>17</v>
@@ -4868,25 +4904,25 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>95</v>
+        <v>284</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>26</v>
@@ -4903,7 +4939,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>42</v>
@@ -4915,22 +4951,22 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>25</v>
@@ -4950,7 +4986,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>42</v>
@@ -4959,34 +4995,34 @@
         <v>17</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>39</v>
@@ -4997,10 +5033,10 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>42</v>
+        <v>241</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>17</v>
@@ -5009,22 +5045,22 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>25</v>
@@ -5044,37 +5080,37 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>95</v>
+        <v>307</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>26</v>
@@ -5091,37 +5127,37 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>26</v>
@@ -5138,10 +5174,10 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>17</v>
@@ -5150,22 +5186,22 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>37</v>
@@ -5185,10 +5221,10 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>17</v>
@@ -5197,31 +5233,31 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>46</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>39</v>
@@ -5232,22 +5268,22 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>21</v>
@@ -5256,13 +5292,13 @@
         <v>35</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>95</v>
+        <v>248</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>26</v>
@@ -5279,10 +5315,10 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
@@ -5291,22 +5327,22 @@
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>37</v>
@@ -5326,10 +5362,10 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>17</v>
@@ -5338,31 +5374,31 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>46</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>39</v>
@@ -5373,43 +5409,43 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>93</v>
+        <v>330</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>39</v>
@@ -5420,10 +5456,10 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>17</v>
@@ -5432,22 +5468,22 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>25</v>
@@ -5467,37 +5503,37 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>95</v>
+        <v>336</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>26</v>
@@ -5514,10 +5550,10 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>17</v>
@@ -5526,25 +5562,25 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>26</v>
@@ -5561,10 +5597,10 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>17</v>
@@ -5573,31 +5609,31 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>95</v>
+        <v>249</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>39</v>
@@ -5608,10 +5644,10 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>17</v>
@@ -5620,31 +5656,31 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>39</v>
@@ -5655,10 +5691,10 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>17</v>
@@ -5667,22 +5703,22 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>25</v>
@@ -5702,34 +5738,34 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>37</v>
@@ -5749,34 +5785,34 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>37</v>
@@ -5796,34 +5832,34 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>37</v>
@@ -5843,34 +5879,34 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>37</v>
@@ -5890,7 +5926,7 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>42</v>
@@ -5899,34 +5935,34 @@
         <v>17</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>95</v>
+        <v>307</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>39</v>
@@ -5937,10 +5973,10 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>17</v>
@@ -5949,31 +5985,31 @@
         <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>37</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>39</v>
@@ -5984,10 +6020,10 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>272</v>
+        <v>103</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>17</v>
@@ -5996,25 +6032,25 @@
         <v>18</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>351</v>
+        <v>111</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>26</v>
@@ -6031,34 +6067,34 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>354</v>
+        <v>241</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>25</v>
@@ -6067,7 +6103,7 @@
         <v>26</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>214</v>
+        <v>27</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>39</v>
@@ -6078,10 +6114,10 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>17</v>
@@ -6090,22 +6126,22 @@
         <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>360</v>
+        <v>307</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>37</v>
@@ -6120,7 +6156,7 @@
         <v>28</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -6136,23 +6172,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B2" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D2" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="E2" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6160,16 +6196,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6177,18 +6213,18 @@
         <v>95</v>
       </c>
       <c r="D5" s="5">
-        <v>0.02666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>33.51</v>
+        <v>27.41</v>
       </c>
       <c r="J5" s="4">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6209,7 +6245,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6240,12 +6276,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B2">
         <v>95</v>
@@ -6253,49 +6289,49 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.02666666666666667</v>
+        <v>0</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>33.51</v>
+        <v>27.41</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B10">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -6304,16 +6340,16 @@
         <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>214</v>
+        <v>391</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>26</v>
@@ -6325,18 +6361,18 @@
         <v>28</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11">
         <v>11</v>
@@ -6351,10 +6387,10 @@
         <v>27</v>
       </c>
       <c r="K11">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="M11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="N11">
         <v>8</v>
@@ -6363,18 +6399,18 @@
         <v>59</v>
       </c>
       <c r="Q11">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>272</v>
+        <v>48</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -6386,45 +6422,45 @@
         <v>59</v>
       </c>
       <c r="J12" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="K12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="N12">
         <v>3</v>
       </c>
       <c r="P12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Q12">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N13">
         <v>7</v>
@@ -6433,24 +6469,24 @@
         <v>39</v>
       </c>
       <c r="Q13">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6461,16 +6497,22 @@
       <c r="N14">
         <v>6</v>
       </c>
+      <c r="P14" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -6478,13 +6520,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6492,13 +6534,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6506,29 +6548,29 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>333</v>
+        <v>113</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>354</v>
+        <v>241</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>0</v>
@@ -6537,150 +6579,186 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
       <c r="D21" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F21" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2</v>
+      </c>
       <c r="D22" s="2" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F22" s="2">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2</v>
+      </c>
       <c r="D23" s="2" t="s">
-        <v>199</v>
+        <v>100</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="F23" s="2">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
       <c r="D24" s="2" t="s">
-        <v>243</v>
+        <v>102</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="F24" s="2">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
       <c r="D25" s="2" t="s">
-        <v>253</v>
+        <v>117</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F25" s="2">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1</v>
+      </c>
       <c r="D26" s="2" t="s">
-        <v>298</v>
+        <v>124</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="F26" s="2">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>299</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>308</v>
+        <v>130</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F27" s="2">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>309</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>322</v>
+        <v>134</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="F28" s="2">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>323</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>337</v>
+        <v>205</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="F29" s="2">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>338</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>337</v>
+        <v>223</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F30" s="2">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>340</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
